--- a/ETF Composition DB/SPY_composition_2026-03-12.xlsx
+++ b/ETF Composition DB/SPY_composition_2026-03-12.xlsx
@@ -6640,7 +6640,7 @@
         <v>1535</v>
       </c>
       <c r="N2" s="5">
-        <v>778.4902</v>
+        <v>0.07784901999999999</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>622</v>
@@ -6693,7 +6693,7 @@
         <v>1536</v>
       </c>
       <c r="N3" s="9">
-        <v>661.0918</v>
+        <v>0.06610918</v>
       </c>
       <c r="O3" s="6" t="s">
         <v>622</v>
@@ -6746,7 +6746,7 @@
         <v>1537</v>
       </c>
       <c r="N4" s="5">
-        <v>522.4708000000001</v>
+        <v>0.05224707999999999</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>622</v>
@@ -6799,7 +6799,7 @@
         <v>1538</v>
       </c>
       <c r="N5" s="9">
-        <v>356.5529</v>
+        <v>0.03565529</v>
       </c>
       <c r="O5" s="6" t="s">
         <v>622</v>
@@ -6852,7 +6852,7 @@
         <v>1539</v>
       </c>
       <c r="N6" s="5">
-        <v>308.9234</v>
+        <v>0.03089234</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>622</v>
@@ -6905,7 +6905,7 @@
         <v>1540</v>
       </c>
       <c r="N7" s="9">
-        <v>277.5264</v>
+        <v>0.02775264</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>622</v>
@@ -6958,7 +6958,7 @@
         <v>1541</v>
       </c>
       <c r="N8" s="5">
-        <v>246.6254</v>
+        <v>0.02466254</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>622</v>
@@ -7011,7 +7011,7 @@
         <v>1542</v>
       </c>
       <c r="N9" s="9">
-        <v>243.1192</v>
+        <v>0.02431192</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>622</v>
@@ -7064,7 +7064,7 @@
         <v>1543</v>
       </c>
       <c r="N10" s="5">
-        <v>194.1499</v>
+        <v>0.01941499</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>622</v>
@@ -7117,7 +7117,7 @@
         <v>1544</v>
       </c>
       <c r="N11" s="9">
-        <v>157.7688</v>
+        <v>0.01577688</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>622</v>
@@ -7170,7 +7170,7 @@
         <v>1545</v>
       </c>
       <c r="N12" s="5">
-        <v>135.7811</v>
+        <v>0.01357811</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>622</v>
@@ -7223,7 +7223,7 @@
         <v>1546</v>
       </c>
       <c r="N13" s="9">
-        <v>134.6989</v>
+        <v>0.01346989</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>622</v>
@@ -7276,7 +7276,7 @@
         <v>1547</v>
       </c>
       <c r="N14" s="5">
-        <v>113.2773</v>
+        <v>0.01132773</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>622</v>
@@ -7329,7 +7329,7 @@
         <v>1548</v>
       </c>
       <c r="N15" s="9">
-        <v>102.0233</v>
+        <v>0.01020233</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>622</v>
@@ -7382,7 +7382,7 @@
         <v>1549</v>
       </c>
       <c r="N16" s="5">
-        <v>96.15049999999999</v>
+        <v>0.00961505</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>622</v>
@@ -7435,7 +7435,7 @@
         <v>1550</v>
       </c>
       <c r="N17" s="9">
-        <v>90.4956</v>
+        <v>0.00904956</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>622</v>
@@ -7488,7 +7488,7 @@
         <v>1551</v>
       </c>
       <c r="N18" s="5">
-        <v>79.5971</v>
+        <v>0.00795971</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>622</v>
@@ -7541,7 +7541,7 @@
         <v>1552</v>
       </c>
       <c r="N19" s="9">
-        <v>77.7891</v>
+        <v>0.00777891</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>622</v>
@@ -7594,7 +7594,7 @@
         <v>1553</v>
       </c>
       <c r="N20" s="5">
-        <v>71.3372</v>
+        <v>0.00713372</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>622</v>
@@ -7647,7 +7647,7 @@
         <v>1554</v>
       </c>
       <c r="N21" s="9">
-        <v>69.9057</v>
+        <v>0.006990570000000001</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>622</v>
@@ -7700,7 +7700,7 @@
         <v>1555</v>
       </c>
       <c r="N22" s="5">
-        <v>69.65770000000001</v>
+        <v>0.00696577</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>622</v>
@@ -7753,7 +7753,7 @@
         <v>1556</v>
       </c>
       <c r="N23" s="9">
-        <v>65.2146</v>
+        <v>0.00652146</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>622</v>
@@ -7806,7 +7806,7 @@
         <v>1557</v>
       </c>
       <c r="N24" s="5">
-        <v>61.5203</v>
+        <v>0.00615203</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>622</v>
@@ -7859,7 +7859,7 @@
         <v>1558</v>
       </c>
       <c r="N25" s="9">
-        <v>61.3348</v>
+        <v>0.00613348</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>622</v>
@@ -7912,7 +7912,7 @@
         <v>1559</v>
       </c>
       <c r="N26" s="5">
-        <v>58.9989</v>
+        <v>0.00589989</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>622</v>
@@ -7965,7 +7965,7 @@
         <v>1560</v>
       </c>
       <c r="N27" s="9">
-        <v>57.3584</v>
+        <v>0.00573584</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>622</v>
@@ -8018,7 +8018,7 @@
         <v>1561</v>
       </c>
       <c r="N28" s="5">
-        <v>56.5901</v>
+        <v>0.00565901</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>622</v>
@@ -8071,7 +8071,7 @@
         <v>1562</v>
       </c>
       <c r="N29" s="9">
-        <v>56.3128</v>
+        <v>0.00563128</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>622</v>
@@ -8124,7 +8124,7 @@
         <v>1563</v>
       </c>
       <c r="N30" s="5">
-        <v>55.3898</v>
+        <v>0.00553898</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>622</v>
@@ -8177,7 +8177,7 @@
         <v>1564</v>
       </c>
       <c r="N31" s="9">
-        <v>53.5889</v>
+        <v>0.00535889</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>622</v>
@@ -8230,7 +8230,7 @@
         <v>1565</v>
       </c>
       <c r="N32" s="5">
-        <v>52.1985</v>
+        <v>0.005219850000000001</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>622</v>
@@ -8283,7 +8283,7 @@
         <v>1566</v>
       </c>
       <c r="N33" s="9">
-        <v>50.323</v>
+        <v>0.0050323</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>622</v>
@@ -8336,7 +8336,7 @@
         <v>1567</v>
       </c>
       <c r="N34" s="5">
-        <v>47.6344</v>
+        <v>0.00476344</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>622</v>
@@ -8389,7 +8389,7 @@
         <v>1568</v>
       </c>
       <c r="N35" s="9">
-        <v>46.9941</v>
+        <v>0.00469941</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>622</v>
@@ -8442,7 +8442,7 @@
         <v>1569</v>
       </c>
       <c r="N36" s="5">
-        <v>46.8325</v>
+        <v>0.00468325</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>622</v>
@@ -8495,7 +8495,7 @@
         <v>1570</v>
       </c>
       <c r="N37" s="9">
-        <v>46.8209</v>
+        <v>0.00468209</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>622</v>
@@ -8548,7 +8548,7 @@
         <v>1571</v>
       </c>
       <c r="N38" s="5">
-        <v>46.0237</v>
+        <v>0.00460237</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>622</v>
@@ -8601,7 +8601,7 @@
         <v>1572</v>
       </c>
       <c r="N39" s="9">
-        <v>43.8806</v>
+        <v>0.00438806</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>622</v>
@@ -8654,7 +8654,7 @@
         <v>1573</v>
       </c>
       <c r="N40" s="5">
-        <v>41.3185</v>
+        <v>0.00413185</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>622</v>
@@ -8707,7 +8707,7 @@
         <v>1574</v>
       </c>
       <c r="N41" s="9">
-        <v>41.3138</v>
+        <v>0.00413138</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>622</v>
@@ -8760,7 +8760,7 @@
         <v>1575</v>
       </c>
       <c r="N42" s="5">
-        <v>40.4948</v>
+        <v>0.004049479999999999</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>622</v>
@@ -8813,7 +8813,7 @@
         <v>1576</v>
       </c>
       <c r="N43" s="9">
-        <v>40.3449</v>
+        <v>0.00403449</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>622</v>
@@ -8866,7 +8866,7 @@
         <v>1577</v>
       </c>
       <c r="N44" s="5">
-        <v>40.0502</v>
+        <v>0.004005020000000001</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>622</v>
@@ -8919,7 +8919,7 @@
         <v>1578</v>
       </c>
       <c r="N45" s="9">
-        <v>39.4843</v>
+        <v>0.00394843</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>622</v>
@@ -8972,7 +8972,7 @@
         <v>1579</v>
       </c>
       <c r="N46" s="5">
-        <v>37.9909</v>
+        <v>0.00379909</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>622</v>
@@ -9025,7 +9025,7 @@
         <v>1580</v>
       </c>
       <c r="N47" s="9">
-        <v>37.3483</v>
+        <v>0.00373483</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>622</v>
@@ -9078,7 +9078,7 @@
         <v>1581</v>
       </c>
       <c r="N48" s="5">
-        <v>35.4847</v>
+        <v>0.00354847</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>622</v>
@@ -9131,7 +9131,7 @@
         <v>1582</v>
       </c>
       <c r="N49" s="9">
-        <v>34.6353</v>
+        <v>0.00346353</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>622</v>
@@ -9184,7 +9184,7 @@
         <v>1583</v>
       </c>
       <c r="N50" s="5">
-        <v>33.9587</v>
+        <v>0.00339587</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>622</v>
@@ -9237,7 +9237,7 @@
         <v>1584</v>
       </c>
       <c r="N51" s="9">
-        <v>33.4082</v>
+        <v>0.00334082</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>622</v>
@@ -9290,7 +9290,7 @@
         <v>1585</v>
       </c>
       <c r="N52" s="5">
-        <v>33.1659</v>
+        <v>0.00331659</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>622</v>
@@ -9343,7 +9343,7 @@
         <v>1586</v>
       </c>
       <c r="N53" s="9">
-        <v>33.0141</v>
+        <v>0.00330141</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>622</v>
@@ -9396,7 +9396,7 @@
         <v>1587</v>
       </c>
       <c r="N54" s="5">
-        <v>32.8848</v>
+        <v>0.00328848</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>622</v>
@@ -9449,7 +9449,7 @@
         <v>1588</v>
       </c>
       <c r="N55" s="9">
-        <v>32.6103</v>
+        <v>0.00326103</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>622</v>
@@ -9502,7 +9502,7 @@
         <v>1589</v>
       </c>
       <c r="N56" s="5">
-        <v>32.3764</v>
+        <v>0.00323764</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>622</v>
@@ -9555,7 +9555,7 @@
         <v>1590</v>
       </c>
       <c r="N57" s="9">
-        <v>31.3417</v>
+        <v>0.00313417</v>
       </c>
       <c r="O57" s="6" t="s">
         <v>622</v>
@@ -9608,7 +9608,7 @@
         <v>1591</v>
       </c>
       <c r="N58" s="5">
-        <v>31.2384</v>
+        <v>0.00312384</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>622</v>
@@ -9661,7 +9661,7 @@
         <v>1592</v>
       </c>
       <c r="N59" s="9">
-        <v>31.0432</v>
+        <v>0.00310432</v>
       </c>
       <c r="O59" s="6" t="s">
         <v>622</v>
@@ -9714,7 +9714,7 @@
         <v>1593</v>
       </c>
       <c r="N60" s="5">
-        <v>30.3094</v>
+        <v>0.00303094</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>622</v>
@@ -9767,7 +9767,7 @@
         <v>1594</v>
       </c>
       <c r="N61" s="9">
-        <v>30.2003</v>
+        <v>0.00302003</v>
       </c>
       <c r="O61" s="6" t="s">
         <v>622</v>
@@ -9820,7 +9820,7 @@
         <v>1595</v>
       </c>
       <c r="N62" s="5">
-        <v>29.7005</v>
+        <v>0.00297005</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>622</v>
@@ -9873,7 +9873,7 @@
         <v>1596</v>
       </c>
       <c r="N63" s="9">
-        <v>28.3671</v>
+        <v>0.00283671</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>622</v>
@@ -9926,7 +9926,7 @@
         <v>1597</v>
       </c>
       <c r="N64" s="5">
-        <v>28.1325</v>
+        <v>0.00281325</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>622</v>
@@ -9979,7 +9979,7 @@
         <v>1598</v>
       </c>
       <c r="N65" s="9">
-        <v>28.0397</v>
+        <v>0.00280397</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>622</v>
@@ -10032,7 +10032,7 @@
         <v>1599</v>
       </c>
       <c r="N66" s="5">
-        <v>26.7031</v>
+        <v>0.00267031</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>622</v>
@@ -10085,7 +10085,7 @@
         <v>1600</v>
       </c>
       <c r="N67" s="9">
-        <v>26.6409</v>
+        <v>0.00266409</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>622</v>
@@ -10138,7 +10138,7 @@
         <v>1601</v>
       </c>
       <c r="N68" s="5">
-        <v>26.5026</v>
+        <v>0.00265026</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>622</v>
@@ -10191,7 +10191,7 @@
         <v>1602</v>
       </c>
       <c r="N69" s="9">
-        <v>26.4234</v>
+        <v>0.00264234</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>622</v>
@@ -10244,7 +10244,7 @@
         <v>1603</v>
       </c>
       <c r="N70" s="5">
-        <v>25.9732</v>
+        <v>0.00259732</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>622</v>
@@ -10297,7 +10297,7 @@
         <v>1604</v>
       </c>
       <c r="N71" s="9">
-        <v>25.9216</v>
+        <v>0.00259216</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>622</v>
@@ -10350,7 +10350,7 @@
         <v>1605</v>
       </c>
       <c r="N72" s="5">
-        <v>25.7412</v>
+        <v>0.00257412</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>622</v>
@@ -10403,7 +10403,7 @@
         <v>1606</v>
       </c>
       <c r="N73" s="9">
-        <v>25.3164</v>
+        <v>0.00253164</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>622</v>
@@ -10456,7 +10456,7 @@
         <v>1607</v>
       </c>
       <c r="N74" s="5">
-        <v>24.7353</v>
+        <v>0.00247353</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>622</v>
@@ -10509,7 +10509,7 @@
         <v>1608</v>
       </c>
       <c r="N75" s="9">
-        <v>24.5521</v>
+        <v>0.00245521</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>622</v>
@@ -10562,7 +10562,7 @@
         <v>1609</v>
       </c>
       <c r="N76" s="5">
-        <v>24.2089</v>
+        <v>0.00242089</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>622</v>
@@ -10615,7 +10615,7 @@
         <v>1610</v>
       </c>
       <c r="N77" s="9">
-        <v>23.7599</v>
+        <v>0.00237599</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>622</v>
@@ -10668,7 +10668,7 @@
         <v>1611</v>
       </c>
       <c r="N78" s="5">
-        <v>23.669</v>
+        <v>0.0023669</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>622</v>
@@ -10721,7 +10721,7 @@
         <v>1612</v>
       </c>
       <c r="N79" s="9">
-        <v>23.4741</v>
+        <v>0.00234741</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>622</v>
@@ -10774,7 +10774,7 @@
         <v>1613</v>
       </c>
       <c r="N80" s="5">
-        <v>23.3735</v>
+        <v>0.00233735</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>622</v>
@@ -10827,7 +10827,7 @@
         <v>1614</v>
       </c>
       <c r="N81" s="9">
-        <v>23.2924</v>
+        <v>0.00232924</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>622</v>
@@ -10880,7 +10880,7 @@
         <v>1615</v>
       </c>
       <c r="N82" s="5">
-        <v>23.2798</v>
+        <v>0.00232798</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>622</v>
@@ -10933,7 +10933,7 @@
         <v>1616</v>
       </c>
       <c r="N83" s="9">
-        <v>22.7849</v>
+        <v>0.00227849</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>622</v>
@@ -10986,7 +10986,7 @@
         <v>1617</v>
       </c>
       <c r="N84" s="5">
-        <v>21.8345</v>
+        <v>0.00218345</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>622</v>
@@ -11039,7 +11039,7 @@
         <v>1618</v>
       </c>
       <c r="N85" s="9">
-        <v>21.4497</v>
+        <v>0.00214497</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>622</v>
@@ -11092,7 +11092,7 @@
         <v>1619</v>
       </c>
       <c r="N86" s="5">
-        <v>21.277</v>
+        <v>0.0021277</v>
       </c>
       <c r="O86" s="2" t="s">
         <v>622</v>
@@ -11145,7 +11145,7 @@
         <v>1620</v>
       </c>
       <c r="N87" s="9">
-        <v>21.2515</v>
+        <v>0.00212515</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>622</v>
@@ -11198,7 +11198,7 @@
         <v>1621</v>
       </c>
       <c r="N88" s="5">
-        <v>21.2462</v>
+        <v>0.00212462</v>
       </c>
       <c r="O88" s="2" t="s">
         <v>622</v>
@@ -11251,7 +11251,7 @@
         <v>1622</v>
       </c>
       <c r="N89" s="9">
-        <v>21.2445</v>
+        <v>0.00212445</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>622</v>
@@ -11304,7 +11304,7 @@
         <v>1623</v>
       </c>
       <c r="N90" s="5">
-        <v>21.0618</v>
+        <v>0.00210618</v>
       </c>
       <c r="O90" s="2" t="s">
         <v>622</v>
@@ -11357,7 +11357,7 @@
         <v>1624</v>
       </c>
       <c r="N91" s="9">
-        <v>21.0262</v>
+        <v>0.00210262</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>622</v>
@@ -11410,7 +11410,7 @@
         <v>1625</v>
       </c>
       <c r="N92" s="5">
-        <v>20.9733</v>
+        <v>0.00209733</v>
       </c>
       <c r="O92" s="2" t="s">
         <v>622</v>
@@ -11463,7 +11463,7 @@
         <v>1626</v>
       </c>
       <c r="N93" s="9">
-        <v>20.5238</v>
+        <v>0.00205238</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>622</v>
@@ -11516,7 +11516,7 @@
         <v>1627</v>
       </c>
       <c r="N94" s="5">
-        <v>20.466</v>
+        <v>0.0020466</v>
       </c>
       <c r="O94" s="2" t="s">
         <v>622</v>
@@ -11569,7 +11569,7 @@
         <v>1628</v>
       </c>
       <c r="N95" s="9">
-        <v>20.4124</v>
+        <v>0.00204124</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>622</v>
@@ -11622,7 +11622,7 @@
         <v>1629</v>
       </c>
       <c r="N96" s="5">
-        <v>20.2831</v>
+        <v>0.00202831</v>
       </c>
       <c r="O96" s="2" t="s">
         <v>622</v>
@@ -11675,7 +11675,7 @@
         <v>622</v>
       </c>
       <c r="N97" s="9">
-        <v>20.21</v>
+        <v>0.002021</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>622</v>
@@ -11728,7 +11728,7 @@
         <v>1630</v>
       </c>
       <c r="N98" s="5">
-        <v>19.9355</v>
+        <v>0.00199355</v>
       </c>
       <c r="O98" s="2" t="s">
         <v>622</v>
@@ -11781,7 +11781,7 @@
         <v>1631</v>
       </c>
       <c r="N99" s="9">
-        <v>19.9026</v>
+        <v>0.00199026</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>622</v>
@@ -11834,7 +11834,7 @@
         <v>1632</v>
       </c>
       <c r="N100" s="5">
-        <v>19.8788</v>
+        <v>0.00198788</v>
       </c>
       <c r="O100" s="2" t="s">
         <v>622</v>
@@ -11887,7 +11887,7 @@
         <v>1633</v>
       </c>
       <c r="N101" s="9">
-        <v>19.7772</v>
+        <v>0.00197772</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>622</v>
@@ -11940,7 +11940,7 @@
         <v>1634</v>
       </c>
       <c r="N102" s="5">
-        <v>19.7179</v>
+        <v>0.00197179</v>
       </c>
       <c r="O102" s="2" t="s">
         <v>622</v>
@@ -11993,7 +11993,7 @@
         <v>1635</v>
       </c>
       <c r="N103" s="9">
-        <v>19.6481</v>
+        <v>0.00196481</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>622</v>
@@ -12046,7 +12046,7 @@
         <v>1636</v>
       </c>
       <c r="N104" s="5">
-        <v>19.6188</v>
+        <v>0.00196188</v>
       </c>
       <c r="O104" s="2" t="s">
         <v>622</v>
@@ -12099,7 +12099,7 @@
         <v>1637</v>
       </c>
       <c r="N105" s="9">
-        <v>19.4058</v>
+        <v>0.00194058</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>622</v>
@@ -12152,7 +12152,7 @@
         <v>1638</v>
       </c>
       <c r="N106" s="5">
-        <v>19.1966</v>
+        <v>0.00191966</v>
       </c>
       <c r="O106" s="2" t="s">
         <v>622</v>
@@ -12205,7 +12205,7 @@
         <v>1639</v>
       </c>
       <c r="N107" s="9">
-        <v>18.858</v>
+        <v>0.0018858</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>622</v>
@@ -12258,7 +12258,7 @@
         <v>1640</v>
       </c>
       <c r="N108" s="5">
-        <v>18.0563</v>
+        <v>0.00180563</v>
       </c>
       <c r="O108" s="2" t="s">
         <v>622</v>
@@ -12311,7 +12311,7 @@
         <v>1641</v>
       </c>
       <c r="N109" s="9">
-        <v>17.9105</v>
+        <v>0.00179105</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>622</v>
@@ -12364,7 +12364,7 @@
         <v>1642</v>
       </c>
       <c r="N110" s="5">
-        <v>17.7577</v>
+        <v>0.00177577</v>
       </c>
       <c r="O110" s="2" t="s">
         <v>622</v>
@@ -12417,7 +12417,7 @@
         <v>1643</v>
       </c>
       <c r="N111" s="9">
-        <v>17.7183</v>
+        <v>0.00177183</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>622</v>
@@ -12470,7 +12470,7 @@
         <v>1644</v>
       </c>
       <c r="N112" s="5">
-        <v>17.2996</v>
+        <v>0.00172996</v>
       </c>
       <c r="O112" s="2" t="s">
         <v>622</v>
@@ -12523,7 +12523,7 @@
         <v>1645</v>
       </c>
       <c r="N113" s="9">
-        <v>17.1687</v>
+        <v>0.00171687</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>622</v>
@@ -12576,7 +12576,7 @@
         <v>1646</v>
       </c>
       <c r="N114" s="5">
-        <v>16.8873</v>
+        <v>0.00168873</v>
       </c>
       <c r="O114" s="2" t="s">
         <v>622</v>
@@ -12629,7 +12629,7 @@
         <v>1647</v>
       </c>
       <c r="N115" s="9">
-        <v>16.6551</v>
+        <v>0.00166551</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>622</v>
@@ -12682,7 +12682,7 @@
         <v>1648</v>
       </c>
       <c r="N116" s="5">
-        <v>16.4505</v>
+        <v>0.00164505</v>
       </c>
       <c r="O116" s="2" t="s">
         <v>622</v>
@@ -12735,7 +12735,7 @@
         <v>1649</v>
       </c>
       <c r="N117" s="9">
-        <v>16.3809</v>
+        <v>0.00163809</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>622</v>
@@ -12788,7 +12788,7 @@
         <v>1650</v>
       </c>
       <c r="N118" s="5">
-        <v>15.9795</v>
+        <v>0.00159795</v>
       </c>
       <c r="O118" s="2" t="s">
         <v>622</v>
@@ -12841,7 +12841,7 @@
         <v>1651</v>
       </c>
       <c r="N119" s="9">
-        <v>15.838</v>
+        <v>0.0015838</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>622</v>
@@ -12894,7 +12894,7 @@
         <v>1652</v>
       </c>
       <c r="N120" s="5">
-        <v>15.7721</v>
+        <v>0.00157721</v>
       </c>
       <c r="O120" s="2" t="s">
         <v>622</v>
@@ -12947,7 +12947,7 @@
         <v>1653</v>
       </c>
       <c r="N121" s="9">
-        <v>15.6387</v>
+        <v>0.00156387</v>
       </c>
       <c r="O121" s="6" t="s">
         <v>622</v>
@@ -13000,7 +13000,7 @@
         <v>1654</v>
       </c>
       <c r="N122" s="5">
-        <v>15.6158</v>
+        <v>0.00156158</v>
       </c>
       <c r="O122" s="2" t="s">
         <v>622</v>
@@ -13053,7 +13053,7 @@
         <v>1655</v>
       </c>
       <c r="N123" s="9">
-        <v>15.4304</v>
+        <v>0.00154304</v>
       </c>
       <c r="O123" s="6" t="s">
         <v>622</v>
@@ -13106,7 +13106,7 @@
         <v>1656</v>
       </c>
       <c r="N124" s="5">
-        <v>14.8988</v>
+        <v>0.00148988</v>
       </c>
       <c r="O124" s="2" t="s">
         <v>622</v>
@@ -13159,7 +13159,7 @@
         <v>1657</v>
       </c>
       <c r="N125" s="9">
-        <v>14.891</v>
+        <v>0.0014891</v>
       </c>
       <c r="O125" s="6" t="s">
         <v>622</v>
@@ -13212,7 +13212,7 @@
         <v>1658</v>
       </c>
       <c r="N126" s="5">
-        <v>14.7846</v>
+        <v>0.00147846</v>
       </c>
       <c r="O126" s="2" t="s">
         <v>622</v>
@@ -13265,7 +13265,7 @@
         <v>1659</v>
       </c>
       <c r="N127" s="9">
-        <v>14.7083</v>
+        <v>0.00147083</v>
       </c>
       <c r="O127" s="6" t="s">
         <v>622</v>
@@ -13318,7 +13318,7 @@
         <v>1660</v>
       </c>
       <c r="N128" s="5">
-        <v>14.6609</v>
+        <v>0.00146609</v>
       </c>
       <c r="O128" s="2" t="s">
         <v>622</v>
@@ -13371,7 +13371,7 @@
         <v>1661</v>
       </c>
       <c r="N129" s="9">
-        <v>14.5731</v>
+        <v>0.00145731</v>
       </c>
       <c r="O129" s="6" t="s">
         <v>622</v>
@@ -13424,7 +13424,7 @@
         <v>1662</v>
       </c>
       <c r="N130" s="5">
-        <v>14.3033</v>
+        <v>0.00143033</v>
       </c>
       <c r="O130" s="2" t="s">
         <v>622</v>
@@ -13477,7 +13477,7 @@
         <v>1663</v>
       </c>
       <c r="N131" s="9">
-        <v>14.2693</v>
+        <v>0.00142693</v>
       </c>
       <c r="O131" s="6" t="s">
         <v>622</v>
@@ -13530,7 +13530,7 @@
         <v>1664</v>
       </c>
       <c r="N132" s="5">
-        <v>14.0141</v>
+        <v>0.00140141</v>
       </c>
       <c r="O132" s="2" t="s">
         <v>622</v>
@@ -13583,7 +13583,7 @@
         <v>1665</v>
       </c>
       <c r="N133" s="9">
-        <v>13.9907</v>
+        <v>0.00139907</v>
       </c>
       <c r="O133" s="6" t="s">
         <v>622</v>
@@ -13636,7 +13636,7 @@
         <v>1666</v>
       </c>
       <c r="N134" s="5">
-        <v>13.9199</v>
+        <v>0.00139199</v>
       </c>
       <c r="O134" s="2" t="s">
         <v>622</v>
@@ -13689,7 +13689,7 @@
         <v>1667</v>
       </c>
       <c r="N135" s="9">
-        <v>13.8709</v>
+        <v>0.00138709</v>
       </c>
       <c r="O135" s="6" t="s">
         <v>622</v>
@@ -13742,7 +13742,7 @@
         <v>1668</v>
       </c>
       <c r="N136" s="5">
-        <v>13.8149</v>
+        <v>0.00138149</v>
       </c>
       <c r="O136" s="2" t="s">
         <v>622</v>
@@ -13795,7 +13795,7 @@
         <v>1669</v>
       </c>
       <c r="N137" s="9">
-        <v>13.7449</v>
+        <v>0.00137449</v>
       </c>
       <c r="O137" s="6" t="s">
         <v>622</v>
@@ -13848,7 +13848,7 @@
         <v>1670</v>
       </c>
       <c r="N138" s="5">
-        <v>13.6212</v>
+        <v>0.00136212</v>
       </c>
       <c r="O138" s="2" t="s">
         <v>622</v>
@@ -13901,7 +13901,7 @@
         <v>1671</v>
       </c>
       <c r="N139" s="9">
-        <v>13.5022</v>
+        <v>0.00135022</v>
       </c>
       <c r="O139" s="6" t="s">
         <v>622</v>
@@ -13954,7 +13954,7 @@
         <v>1672</v>
       </c>
       <c r="N140" s="5">
-        <v>13.4216</v>
+        <v>0.00134216</v>
       </c>
       <c r="O140" s="2" t="s">
         <v>622</v>
@@ -14007,7 +14007,7 @@
         <v>1673</v>
       </c>
       <c r="N141" s="9">
-        <v>13.1905</v>
+        <v>0.00131905</v>
       </c>
       <c r="O141" s="6" t="s">
         <v>622</v>
@@ -14060,7 +14060,7 @@
         <v>1674</v>
       </c>
       <c r="N142" s="5">
-        <v>13.1769</v>
+        <v>0.00131769</v>
       </c>
       <c r="O142" s="2" t="s">
         <v>622</v>
@@ -14113,7 +14113,7 @@
         <v>1675</v>
       </c>
       <c r="N143" s="9">
-        <v>12.9866</v>
+        <v>0.00129866</v>
       </c>
       <c r="O143" s="6" t="s">
         <v>622</v>
@@ -14166,7 +14166,7 @@
         <v>1676</v>
       </c>
       <c r="N144" s="5">
-        <v>12.9825</v>
+        <v>0.00129825</v>
       </c>
       <c r="O144" s="2" t="s">
         <v>622</v>
@@ -14219,7 +14219,7 @@
         <v>1677</v>
       </c>
       <c r="N145" s="9">
-        <v>12.8265</v>
+        <v>0.00128265</v>
       </c>
       <c r="O145" s="6" t="s">
         <v>622</v>
@@ -14272,7 +14272,7 @@
         <v>1678</v>
       </c>
       <c r="N146" s="5">
-        <v>12.7597</v>
+        <v>0.00127597</v>
       </c>
       <c r="O146" s="2" t="s">
         <v>622</v>
@@ -14325,7 +14325,7 @@
         <v>1679</v>
       </c>
       <c r="N147" s="9">
-        <v>12.6489</v>
+        <v>0.00126489</v>
       </c>
       <c r="O147" s="6" t="s">
         <v>622</v>
@@ -14378,7 +14378,7 @@
         <v>1680</v>
       </c>
       <c r="N148" s="5">
-        <v>12.6424</v>
+        <v>0.00126424</v>
       </c>
       <c r="O148" s="2" t="s">
         <v>622</v>
@@ -14431,7 +14431,7 @@
         <v>1681</v>
       </c>
       <c r="N149" s="9">
-        <v>12.5957</v>
+        <v>0.00125957</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>622</v>
@@ -14484,7 +14484,7 @@
         <v>1682</v>
       </c>
       <c r="N150" s="5">
-        <v>12.4334</v>
+        <v>0.00124334</v>
       </c>
       <c r="O150" s="2" t="s">
         <v>622</v>
@@ -14537,7 +14537,7 @@
         <v>1683</v>
       </c>
       <c r="N151" s="9">
-        <v>12.4154</v>
+        <v>0.00124154</v>
       </c>
       <c r="O151" s="6" t="s">
         <v>622</v>
@@ -14590,7 +14590,7 @@
         <v>1684</v>
       </c>
       <c r="N152" s="5">
-        <v>12.3689</v>
+        <v>0.00123689</v>
       </c>
       <c r="O152" s="2" t="s">
         <v>622</v>
@@ -14643,7 +14643,7 @@
         <v>1685</v>
       </c>
       <c r="N153" s="9">
-        <v>12.338</v>
+        <v>0.0012338</v>
       </c>
       <c r="O153" s="6" t="s">
         <v>622</v>
@@ -14696,7 +14696,7 @@
         <v>1686</v>
       </c>
       <c r="N154" s="5">
-        <v>12.2863</v>
+        <v>0.00122863</v>
       </c>
       <c r="O154" s="2" t="s">
         <v>622</v>
@@ -14749,7 +14749,7 @@
         <v>1687</v>
       </c>
       <c r="N155" s="9">
-        <v>12.2818</v>
+        <v>0.00122818</v>
       </c>
       <c r="O155" s="6" t="s">
         <v>622</v>
@@ -14802,7 +14802,7 @@
         <v>1688</v>
       </c>
       <c r="N156" s="5">
-        <v>12.28</v>
+        <v>0.001228</v>
       </c>
       <c r="O156" s="2" t="s">
         <v>622</v>
@@ -14855,7 +14855,7 @@
         <v>1689</v>
       </c>
       <c r="N157" s="9">
-        <v>12.255</v>
+        <v>0.0012255</v>
       </c>
       <c r="O157" s="6" t="s">
         <v>622</v>
@@ -14908,7 +14908,7 @@
         <v>1690</v>
       </c>
       <c r="N158" s="5">
-        <v>12.112</v>
+        <v>0.0012112</v>
       </c>
       <c r="O158" s="2" t="s">
         <v>622</v>
@@ -14961,7 +14961,7 @@
         <v>1691</v>
       </c>
       <c r="N159" s="9">
-        <v>12.0805</v>
+        <v>0.00120805</v>
       </c>
       <c r="O159" s="6" t="s">
         <v>622</v>
@@ -15014,7 +15014,7 @@
         <v>1692</v>
       </c>
       <c r="N160" s="5">
-        <v>11.9995</v>
+        <v>0.00119995</v>
       </c>
       <c r="O160" s="2" t="s">
         <v>622</v>
@@ -15067,7 +15067,7 @@
         <v>1693</v>
       </c>
       <c r="N161" s="9">
-        <v>11.9783</v>
+        <v>0.00119783</v>
       </c>
       <c r="O161" s="6" t="s">
         <v>622</v>
@@ -15120,7 +15120,7 @@
         <v>1694</v>
       </c>
       <c r="N162" s="5">
-        <v>11.9739</v>
+        <v>0.00119739</v>
       </c>
       <c r="O162" s="2" t="s">
         <v>622</v>
@@ -15173,7 +15173,7 @@
         <v>1695</v>
       </c>
       <c r="N163" s="9">
-        <v>11.9259</v>
+        <v>0.00119259</v>
       </c>
       <c r="O163" s="6" t="s">
         <v>622</v>
@@ -15226,7 +15226,7 @@
         <v>1696</v>
       </c>
       <c r="N164" s="5">
-        <v>11.8916</v>
+        <v>0.00118916</v>
       </c>
       <c r="O164" s="2" t="s">
         <v>622</v>
@@ -15279,7 +15279,7 @@
         <v>1697</v>
       </c>
       <c r="N165" s="9">
-        <v>11.8915</v>
+        <v>0.00118915</v>
       </c>
       <c r="O165" s="6" t="s">
         <v>622</v>
@@ -15332,7 +15332,7 @@
         <v>1698</v>
       </c>
       <c r="N166" s="5">
-        <v>11.7978</v>
+        <v>0.00117978</v>
       </c>
       <c r="O166" s="2" t="s">
         <v>622</v>
@@ -15385,7 +15385,7 @@
         <v>1699</v>
       </c>
       <c r="N167" s="9">
-        <v>11.7936</v>
+        <v>0.00117936</v>
       </c>
       <c r="O167" s="6" t="s">
         <v>622</v>
@@ -15438,7 +15438,7 @@
         <v>1700</v>
       </c>
       <c r="N168" s="5">
-        <v>11.7065</v>
+        <v>0.00117065</v>
       </c>
       <c r="O168" s="2" t="s">
         <v>622</v>
@@ -15491,7 +15491,7 @@
         <v>1701</v>
       </c>
       <c r="N169" s="9">
-        <v>11.7031</v>
+        <v>0.00117031</v>
       </c>
       <c r="O169" s="6" t="s">
         <v>622</v>
@@ -15544,7 +15544,7 @@
         <v>1702</v>
       </c>
       <c r="N170" s="5">
-        <v>11.6424</v>
+        <v>0.00116424</v>
       </c>
       <c r="O170" s="2" t="s">
         <v>622</v>
@@ -15597,7 +15597,7 @@
         <v>1703</v>
       </c>
       <c r="N171" s="9">
-        <v>11.5612</v>
+        <v>0.00115612</v>
       </c>
       <c r="O171" s="6" t="s">
         <v>622</v>
@@ -15650,7 +15650,7 @@
         <v>1704</v>
       </c>
       <c r="N172" s="5">
-        <v>11.459</v>
+        <v>0.0011459</v>
       </c>
       <c r="O172" s="2" t="s">
         <v>622</v>
@@ -15703,7 +15703,7 @@
         <v>1705</v>
       </c>
       <c r="N173" s="9">
-        <v>11.446</v>
+        <v>0.0011446</v>
       </c>
       <c r="O173" s="6" t="s">
         <v>622</v>
@@ -15756,7 +15756,7 @@
         <v>1706</v>
       </c>
       <c r="N174" s="5">
-        <v>11.4246</v>
+        <v>0.00114246</v>
       </c>
       <c r="O174" s="2" t="s">
         <v>622</v>
@@ -15809,7 +15809,7 @@
         <v>1707</v>
       </c>
       <c r="N175" s="9">
-        <v>11.3239</v>
+        <v>0.00113239</v>
       </c>
       <c r="O175" s="6" t="s">
         <v>622</v>
@@ -15862,7 +15862,7 @@
         <v>1708</v>
       </c>
       <c r="N176" s="5">
-        <v>11.2474</v>
+        <v>0.00112474</v>
       </c>
       <c r="O176" s="2" t="s">
         <v>622</v>
@@ -15915,7 +15915,7 @@
         <v>1709</v>
       </c>
       <c r="N177" s="9">
-        <v>11.2034</v>
+        <v>0.00112034</v>
       </c>
       <c r="O177" s="6" t="s">
         <v>622</v>
@@ -15968,7 +15968,7 @@
         <v>1710</v>
       </c>
       <c r="N178" s="5">
-        <v>10.7269</v>
+        <v>0.00107269</v>
       </c>
       <c r="O178" s="2" t="s">
         <v>622</v>
@@ -16021,7 +16021,7 @@
         <v>1711</v>
       </c>
       <c r="N179" s="9">
-        <v>10.7268</v>
+        <v>0.00107268</v>
       </c>
       <c r="O179" s="6" t="s">
         <v>622</v>
@@ -16074,7 +16074,7 @@
         <v>1712</v>
       </c>
       <c r="N180" s="5">
-        <v>10.6347</v>
+        <v>0.00106347</v>
       </c>
       <c r="O180" s="2" t="s">
         <v>622</v>
@@ -16127,7 +16127,7 @@
         <v>1713</v>
       </c>
       <c r="N181" s="9">
-        <v>10.5894</v>
+        <v>0.00105894</v>
       </c>
       <c r="O181" s="6" t="s">
         <v>622</v>
@@ -16180,7 +16180,7 @@
         <v>1714</v>
       </c>
       <c r="N182" s="5">
-        <v>10.5234</v>
+        <v>0.00105234</v>
       </c>
       <c r="O182" s="2" t="s">
         <v>622</v>
@@ -16233,7 +16233,7 @@
         <v>1715</v>
       </c>
       <c r="N183" s="9">
-        <v>10.4827</v>
+        <v>0.00104827</v>
       </c>
       <c r="O183" s="6" t="s">
         <v>622</v>
@@ -16286,7 +16286,7 @@
         <v>1716</v>
       </c>
       <c r="N184" s="5">
-        <v>10.4764</v>
+        <v>0.00104764</v>
       </c>
       <c r="O184" s="2" t="s">
         <v>622</v>
@@ -16339,7 +16339,7 @@
         <v>1717</v>
       </c>
       <c r="N185" s="9">
-        <v>10.193</v>
+        <v>0.0010193</v>
       </c>
       <c r="O185" s="6" t="s">
         <v>622</v>
@@ -16392,7 +16392,7 @@
         <v>1718</v>
       </c>
       <c r="N186" s="5">
-        <v>10.1322</v>
+        <v>0.00101322</v>
       </c>
       <c r="O186" s="2" t="s">
         <v>622</v>
@@ -16445,7 +16445,7 @@
         <v>1719</v>
       </c>
       <c r="N187" s="9">
-        <v>10.0832</v>
+        <v>0.00100832</v>
       </c>
       <c r="O187" s="6" t="s">
         <v>622</v>
@@ -16498,7 +16498,7 @@
         <v>1720</v>
       </c>
       <c r="N188" s="5">
-        <v>9.940300000000001</v>
+        <v>0.0009940300000000001</v>
       </c>
       <c r="O188" s="2" t="s">
         <v>622</v>
@@ -16551,7 +16551,7 @@
         <v>1721</v>
       </c>
       <c r="N189" s="9">
-        <v>9.6503</v>
+        <v>0.0009650300000000001</v>
       </c>
       <c r="O189" s="6" t="s">
         <v>622</v>
@@ -16604,7 +16604,7 @@
         <v>1722</v>
       </c>
       <c r="N190" s="5">
-        <v>9.6091</v>
+        <v>0.0009609099999999999</v>
       </c>
       <c r="O190" s="2" t="s">
         <v>622</v>
@@ -16657,7 +16657,7 @@
         <v>1723</v>
       </c>
       <c r="N191" s="9">
-        <v>9.511100000000001</v>
+        <v>0.00095111</v>
       </c>
       <c r="O191" s="6" t="s">
         <v>622</v>
@@ -16710,7 +16710,7 @@
         <v>1724</v>
       </c>
       <c r="N192" s="5">
-        <v>9.4375</v>
+        <v>0.00094375</v>
       </c>
       <c r="O192" s="2" t="s">
         <v>622</v>
@@ -16763,7 +16763,7 @@
         <v>1725</v>
       </c>
       <c r="N193" s="9">
-        <v>9.396000000000001</v>
+        <v>0.0009396000000000001</v>
       </c>
       <c r="O193" s="6" t="s">
         <v>622</v>
@@ -16816,7 +16816,7 @@
         <v>1726</v>
       </c>
       <c r="N194" s="5">
-        <v>9.3727</v>
+        <v>0.00093727</v>
       </c>
       <c r="O194" s="2" t="s">
         <v>622</v>
@@ -16869,7 +16869,7 @@
         <v>1727</v>
       </c>
       <c r="N195" s="9">
-        <v>9.343</v>
+        <v>0.0009343</v>
       </c>
       <c r="O195" s="6" t="s">
         <v>622</v>
@@ -16922,7 +16922,7 @@
         <v>1728</v>
       </c>
       <c r="N196" s="5">
-        <v>9.327199999999999</v>
+        <v>0.0009327199999999999</v>
       </c>
       <c r="O196" s="2" t="s">
         <v>622</v>
@@ -16975,7 +16975,7 @@
         <v>1729</v>
       </c>
       <c r="N197" s="9">
-        <v>9.3216</v>
+        <v>0.0009321599999999999</v>
       </c>
       <c r="O197" s="6" t="s">
         <v>622</v>
@@ -17028,7 +17028,7 @@
         <v>1730</v>
       </c>
       <c r="N198" s="5">
-        <v>9.2074</v>
+        <v>0.0009207400000000001</v>
       </c>
       <c r="O198" s="2" t="s">
         <v>622</v>
@@ -17081,7 +17081,7 @@
         <v>1731</v>
       </c>
       <c r="N199" s="9">
-        <v>9.1717</v>
+        <v>0.00091717</v>
       </c>
       <c r="O199" s="6" t="s">
         <v>622</v>
@@ -17134,7 +17134,7 @@
         <v>1732</v>
       </c>
       <c r="N200" s="5">
-        <v>9.116300000000001</v>
+        <v>0.00091163</v>
       </c>
       <c r="O200" s="2" t="s">
         <v>622</v>
@@ -17187,7 +17187,7 @@
         <v>1733</v>
       </c>
       <c r="N201" s="9">
-        <v>9.094900000000001</v>
+        <v>0.00090949</v>
       </c>
       <c r="O201" s="6" t="s">
         <v>622</v>
@@ -17240,7 +17240,7 @@
         <v>1734</v>
       </c>
       <c r="N202" s="5">
-        <v>9.0563</v>
+        <v>0.00090563</v>
       </c>
       <c r="O202" s="2" t="s">
         <v>622</v>
@@ -17293,7 +17293,7 @@
         <v>1735</v>
       </c>
       <c r="N203" s="9">
-        <v>8.920400000000001</v>
+        <v>0.0008920400000000001</v>
       </c>
       <c r="O203" s="6" t="s">
         <v>622</v>
@@ -17346,7 +17346,7 @@
         <v>1736</v>
       </c>
       <c r="N204" s="5">
-        <v>8.9108</v>
+        <v>0.00089108</v>
       </c>
       <c r="O204" s="2" t="s">
         <v>622</v>
@@ -17399,7 +17399,7 @@
         <v>1737</v>
       </c>
       <c r="N205" s="9">
-        <v>8.902699999999999</v>
+        <v>0.00089027</v>
       </c>
       <c r="O205" s="6" t="s">
         <v>622</v>
@@ -17452,7 +17452,7 @@
         <v>1738</v>
       </c>
       <c r="N206" s="5">
-        <v>8.750500000000001</v>
+        <v>0.00087505</v>
       </c>
       <c r="O206" s="2" t="s">
         <v>622</v>
@@ -17505,7 +17505,7 @@
         <v>1739</v>
       </c>
       <c r="N207" s="9">
-        <v>8.691000000000001</v>
+        <v>0.0008691</v>
       </c>
       <c r="O207" s="6" t="s">
         <v>622</v>
@@ -17558,7 +17558,7 @@
         <v>1740</v>
       </c>
       <c r="N208" s="5">
-        <v>8.6532</v>
+        <v>0.0008653199999999999</v>
       </c>
       <c r="O208" s="2" t="s">
         <v>622</v>
@@ -17611,7 +17611,7 @@
         <v>1741</v>
       </c>
       <c r="N209" s="9">
-        <v>8.598699999999999</v>
+        <v>0.00085987</v>
       </c>
       <c r="O209" s="6" t="s">
         <v>622</v>
@@ -17664,7 +17664,7 @@
         <v>1742</v>
       </c>
       <c r="N210" s="5">
-        <v>8.516</v>
+        <v>0.0008516</v>
       </c>
       <c r="O210" s="2" t="s">
         <v>622</v>
@@ -17717,7 +17717,7 @@
         <v>1743</v>
       </c>
       <c r="N211" s="9">
-        <v>8.464600000000001</v>
+        <v>0.0008464599999999999</v>
       </c>
       <c r="O211" s="6" t="s">
         <v>622</v>
@@ -17770,7 +17770,7 @@
         <v>1744</v>
       </c>
       <c r="N212" s="5">
-        <v>8.4034</v>
+        <v>0.00084034</v>
       </c>
       <c r="O212" s="2" t="s">
         <v>622</v>
@@ -17823,7 +17823,7 @@
         <v>1745</v>
       </c>
       <c r="N213" s="9">
-        <v>8.3285</v>
+        <v>0.00083285</v>
       </c>
       <c r="O213" s="6" t="s">
         <v>622</v>
@@ -17876,7 +17876,7 @@
         <v>1746</v>
       </c>
       <c r="N214" s="5">
-        <v>8.3073</v>
+        <v>0.0008307299999999999</v>
       </c>
       <c r="O214" s="2" t="s">
         <v>622</v>
@@ -17929,7 +17929,7 @@
         <v>1747</v>
       </c>
       <c r="N215" s="9">
-        <v>8.291499999999999</v>
+        <v>0.0008291500000000001</v>
       </c>
       <c r="O215" s="6" t="s">
         <v>622</v>
@@ -17982,7 +17982,7 @@
         <v>1748</v>
       </c>
       <c r="N216" s="5">
-        <v>8.241099999999999</v>
+        <v>0.00082411</v>
       </c>
       <c r="O216" s="2" t="s">
         <v>622</v>
@@ -18035,7 +18035,7 @@
         <v>1749</v>
       </c>
       <c r="N217" s="9">
-        <v>8.231999999999999</v>
+        <v>0.0008232000000000001</v>
       </c>
       <c r="O217" s="6" t="s">
         <v>622</v>
@@ -18088,7 +18088,7 @@
         <v>1750</v>
       </c>
       <c r="N218" s="5">
-        <v>8.1775</v>
+        <v>0.00081775</v>
       </c>
       <c r="O218" s="2" t="s">
         <v>622</v>
@@ -18141,7 +18141,7 @@
         <v>1751</v>
       </c>
       <c r="N219" s="9">
-        <v>8.169700000000001</v>
+        <v>0.0008169700000000001</v>
       </c>
       <c r="O219" s="6" t="s">
         <v>622</v>
@@ -18194,7 +18194,7 @@
         <v>1752</v>
       </c>
       <c r="N220" s="5">
-        <v>8.1561</v>
+        <v>0.0008156099999999999</v>
       </c>
       <c r="O220" s="2" t="s">
         <v>622</v>
@@ -18247,7 +18247,7 @@
         <v>1753</v>
       </c>
       <c r="N221" s="9">
-        <v>8.001200000000001</v>
+        <v>0.00080012</v>
       </c>
       <c r="O221" s="6" t="s">
         <v>622</v>
@@ -18300,7 +18300,7 @@
         <v>1754</v>
       </c>
       <c r="N222" s="5">
-        <v>7.9823</v>
+        <v>0.00079823</v>
       </c>
       <c r="O222" s="2" t="s">
         <v>622</v>
@@ -18353,7 +18353,7 @@
         <v>1755</v>
       </c>
       <c r="N223" s="9">
-        <v>7.9622</v>
+        <v>0.0007962199999999999</v>
       </c>
       <c r="O223" s="6" t="s">
         <v>622</v>
@@ -18406,7 +18406,7 @@
         <v>1756</v>
       </c>
       <c r="N224" s="5">
-        <v>7.9564</v>
+        <v>0.0007956399999999999</v>
       </c>
       <c r="O224" s="2" t="s">
         <v>622</v>
@@ -18459,7 +18459,7 @@
         <v>1757</v>
       </c>
       <c r="N225" s="9">
-        <v>7.9124</v>
+        <v>0.00079124</v>
       </c>
       <c r="O225" s="6" t="s">
         <v>622</v>
@@ -18512,7 +18512,7 @@
         <v>1758</v>
       </c>
       <c r="N226" s="5">
-        <v>7.8611</v>
+        <v>0.00078611</v>
       </c>
       <c r="O226" s="2" t="s">
         <v>622</v>
@@ -18565,7 +18565,7 @@
         <v>1759</v>
       </c>
       <c r="N227" s="9">
-        <v>7.832</v>
+        <v>0.0007832</v>
       </c>
       <c r="O227" s="6" t="s">
         <v>622</v>
@@ -18618,7 +18618,7 @@
         <v>1760</v>
       </c>
       <c r="N228" s="5">
-        <v>7.7987</v>
+        <v>0.00077987</v>
       </c>
       <c r="O228" s="2" t="s">
         <v>622</v>
@@ -18671,7 +18671,7 @@
         <v>1761</v>
       </c>
       <c r="N229" s="9">
-        <v>7.721</v>
+        <v>0.0007721</v>
       </c>
       <c r="O229" s="6" t="s">
         <v>622</v>
@@ -18724,7 +18724,7 @@
         <v>1762</v>
       </c>
       <c r="N230" s="5">
-        <v>7.6994</v>
+        <v>0.0007699400000000001</v>
       </c>
       <c r="O230" s="2" t="s">
         <v>622</v>
@@ -18777,7 +18777,7 @@
         <v>1763</v>
       </c>
       <c r="N231" s="9">
-        <v>7.5397</v>
+        <v>0.0007539700000000001</v>
       </c>
       <c r="O231" s="6" t="s">
         <v>622</v>
@@ -18830,7 +18830,7 @@
         <v>1764</v>
       </c>
       <c r="N232" s="5">
-        <v>7.3277</v>
+        <v>0.00073277</v>
       </c>
       <c r="O232" s="2" t="s">
         <v>622</v>
@@ -18883,7 +18883,7 @@
         <v>1765</v>
       </c>
       <c r="N233" s="9">
-        <v>7.2688</v>
+        <v>0.0007268800000000001</v>
       </c>
       <c r="O233" s="6" t="s">
         <v>622</v>
@@ -18936,7 +18936,7 @@
         <v>1766</v>
       </c>
       <c r="N234" s="5">
-        <v>7.2481</v>
+        <v>0.00072481</v>
       </c>
       <c r="O234" s="2" t="s">
         <v>622</v>
@@ -18989,7 +18989,7 @@
         <v>1767</v>
       </c>
       <c r="N235" s="9">
-        <v>7.2473</v>
+        <v>0.0007247299999999999</v>
       </c>
       <c r="O235" s="6" t="s">
         <v>622</v>
@@ -19042,7 +19042,7 @@
         <v>1768</v>
       </c>
       <c r="N236" s="5">
-        <v>7.2271</v>
+        <v>0.00072271</v>
       </c>
       <c r="O236" s="2" t="s">
         <v>622</v>
@@ -19095,7 +19095,7 @@
         <v>1769</v>
       </c>
       <c r="N237" s="9">
-        <v>7.1921</v>
+        <v>0.00071921</v>
       </c>
       <c r="O237" s="6" t="s">
         <v>622</v>
@@ -19148,7 +19148,7 @@
         <v>1770</v>
       </c>
       <c r="N238" s="5">
-        <v>7.1764</v>
+        <v>0.00071764</v>
       </c>
       <c r="O238" s="2" t="s">
         <v>622</v>
@@ -19201,7 +19201,7 @@
         <v>1771</v>
       </c>
       <c r="N239" s="9">
-        <v>7.164</v>
+        <v>0.0007164</v>
       </c>
       <c r="O239" s="6" t="s">
         <v>622</v>
@@ -19254,7 +19254,7 @@
         <v>1772</v>
       </c>
       <c r="N240" s="5">
-        <v>7.1428</v>
+        <v>0.0007142800000000001</v>
       </c>
       <c r="O240" s="2" t="s">
         <v>622</v>
@@ -19307,7 +19307,7 @@
         <v>1773</v>
       </c>
       <c r="N241" s="9">
-        <v>7.1244</v>
+        <v>0.0007124400000000001</v>
       </c>
       <c r="O241" s="6" t="s">
         <v>622</v>
@@ -19360,7 +19360,7 @@
         <v>1774</v>
       </c>
       <c r="N242" s="5">
-        <v>7.0979</v>
+        <v>0.00070979</v>
       </c>
       <c r="O242" s="2" t="s">
         <v>622</v>
@@ -19413,7 +19413,7 @@
         <v>1775</v>
       </c>
       <c r="N243" s="9">
-        <v>7.091</v>
+        <v>0.0007091000000000001</v>
       </c>
       <c r="O243" s="6" t="s">
         <v>622</v>
@@ -19466,7 +19466,7 @@
         <v>1776</v>
       </c>
       <c r="N244" s="5">
-        <v>7.0591</v>
+        <v>0.00070591</v>
       </c>
       <c r="O244" s="2" t="s">
         <v>622</v>
@@ -19519,7 +19519,7 @@
         <v>1777</v>
       </c>
       <c r="N245" s="9">
-        <v>7.0574</v>
+        <v>0.0007057399999999999</v>
       </c>
       <c r="O245" s="6" t="s">
         <v>622</v>
@@ -19572,7 +19572,7 @@
         <v>1778</v>
       </c>
       <c r="N246" s="5">
-        <v>7.0515</v>
+        <v>0.00070515</v>
       </c>
       <c r="O246" s="2" t="s">
         <v>622</v>
@@ -19625,7 +19625,7 @@
         <v>1779</v>
       </c>
       <c r="N247" s="9">
-        <v>6.951</v>
+        <v>0.0006951</v>
       </c>
       <c r="O247" s="6" t="s">
         <v>622</v>
@@ -19678,7 +19678,7 @@
         <v>1780</v>
       </c>
       <c r="N248" s="5">
-        <v>6.8673</v>
+        <v>0.00068673</v>
       </c>
       <c r="O248" s="2" t="s">
         <v>622</v>
@@ -19731,7 +19731,7 @@
         <v>1781</v>
       </c>
       <c r="N249" s="9">
-        <v>6.8569</v>
+        <v>0.0006856900000000001</v>
       </c>
       <c r="O249" s="6" t="s">
         <v>622</v>
@@ -19784,7 +19784,7 @@
         <v>1782</v>
       </c>
       <c r="N250" s="5">
-        <v>6.7666</v>
+        <v>0.00067666</v>
       </c>
       <c r="O250" s="2" t="s">
         <v>622</v>
@@ -19837,7 +19837,7 @@
         <v>1783</v>
       </c>
       <c r="N251" s="9">
-        <v>6.7294</v>
+        <v>0.00067294</v>
       </c>
       <c r="O251" s="6" t="s">
         <v>622</v>
@@ -19890,7 +19890,7 @@
         <v>1784</v>
       </c>
       <c r="N252" s="5">
-        <v>6.6682</v>
+        <v>0.00066682</v>
       </c>
       <c r="O252" s="2" t="s">
         <v>622</v>
@@ -19943,7 +19943,7 @@
         <v>1785</v>
       </c>
       <c r="N253" s="9">
-        <v>6.6675</v>
+        <v>0.00066675</v>
       </c>
       <c r="O253" s="6" t="s">
         <v>622</v>
@@ -19996,7 +19996,7 @@
         <v>1786</v>
       </c>
       <c r="N254" s="5">
-        <v>6.6405</v>
+        <v>0.00066405</v>
       </c>
       <c r="O254" s="2" t="s">
         <v>622</v>
@@ -20049,7 +20049,7 @@
         <v>1787</v>
       </c>
       <c r="N255" s="9">
-        <v>6.6147</v>
+        <v>0.0006614699999999999</v>
       </c>
       <c r="O255" s="6" t="s">
         <v>622</v>
@@ -20102,7 +20102,7 @@
         <v>1788</v>
       </c>
       <c r="N256" s="5">
-        <v>6.5797</v>
+        <v>0.0006579699999999999</v>
       </c>
       <c r="O256" s="2" t="s">
         <v>622</v>
@@ -20155,7 +20155,7 @@
         <v>1789</v>
       </c>
       <c r="N257" s="9">
-        <v>6.5594</v>
+        <v>0.00065594</v>
       </c>
       <c r="O257" s="6" t="s">
         <v>622</v>
@@ -20208,7 +20208,7 @@
         <v>1790</v>
       </c>
       <c r="N258" s="5">
-        <v>6.554</v>
+        <v>0.0006554</v>
       </c>
       <c r="O258" s="2" t="s">
         <v>622</v>
@@ -20261,7 +20261,7 @@
         <v>1791</v>
       </c>
       <c r="N259" s="9">
-        <v>6.5201</v>
+        <v>0.00065201</v>
       </c>
       <c r="O259" s="6" t="s">
         <v>622</v>
@@ -20314,7 +20314,7 @@
         <v>1792</v>
       </c>
       <c r="N260" s="5">
-        <v>6.4705</v>
+        <v>0.00064705</v>
       </c>
       <c r="O260" s="2" t="s">
         <v>622</v>
@@ -20367,7 +20367,7 @@
         <v>1793</v>
       </c>
       <c r="N261" s="9">
-        <v>6.3903</v>
+        <v>0.0006390300000000001</v>
       </c>
       <c r="O261" s="6" t="s">
         <v>622</v>
@@ -20420,7 +20420,7 @@
         <v>1794</v>
       </c>
       <c r="N262" s="5">
-        <v>6.351</v>
+        <v>0.0006351</v>
       </c>
       <c r="O262" s="2" t="s">
         <v>622</v>
@@ -20473,7 +20473,7 @@
         <v>1795</v>
       </c>
       <c r="N263" s="9">
-        <v>6.1997</v>
+        <v>0.00061997</v>
       </c>
       <c r="O263" s="6" t="s">
         <v>622</v>
@@ -20526,7 +20526,7 @@
         <v>1796</v>
       </c>
       <c r="N264" s="5">
-        <v>6.0896</v>
+        <v>0.00060896</v>
       </c>
       <c r="O264" s="2" t="s">
         <v>622</v>
@@ -20579,7 +20579,7 @@
         <v>1797</v>
       </c>
       <c r="N265" s="9">
-        <v>6.0794</v>
+        <v>0.00060794</v>
       </c>
       <c r="O265" s="6" t="s">
         <v>622</v>
@@ -20632,7 +20632,7 @@
         <v>1798</v>
       </c>
       <c r="N266" s="5">
-        <v>6.0268</v>
+        <v>0.00060268</v>
       </c>
       <c r="O266" s="2" t="s">
         <v>622</v>
@@ -20685,7 +20685,7 @@
         <v>1799</v>
       </c>
       <c r="N267" s="9">
-        <v>5.9583</v>
+        <v>0.00059583</v>
       </c>
       <c r="O267" s="6" t="s">
         <v>622</v>
@@ -20738,7 +20738,7 @@
         <v>1800</v>
       </c>
       <c r="N268" s="5">
-        <v>5.9461</v>
+        <v>0.00059461</v>
       </c>
       <c r="O268" s="2" t="s">
         <v>622</v>
@@ -20791,7 +20791,7 @@
         <v>1801</v>
       </c>
       <c r="N269" s="9">
-        <v>5.916</v>
+        <v>0.0005916</v>
       </c>
       <c r="O269" s="6" t="s">
         <v>622</v>
@@ -20844,7 +20844,7 @@
         <v>1802</v>
       </c>
       <c r="N270" s="5">
-        <v>5.8275</v>
+        <v>0.00058275</v>
       </c>
       <c r="O270" s="2" t="s">
         <v>622</v>
@@ -20897,7 +20897,7 @@
         <v>1803</v>
       </c>
       <c r="N271" s="9">
-        <v>5.773</v>
+        <v>0.0005773</v>
       </c>
       <c r="O271" s="6" t="s">
         <v>622</v>
@@ -20950,7 +20950,7 @@
         <v>1804</v>
       </c>
       <c r="N272" s="5">
-        <v>5.764</v>
+        <v>0.0005763999999999999</v>
       </c>
       <c r="O272" s="2" t="s">
         <v>622</v>
@@ -21003,7 +21003,7 @@
         <v>1805</v>
       </c>
       <c r="N273" s="9">
-        <v>5.6825</v>
+        <v>0.00056825</v>
       </c>
       <c r="O273" s="6" t="s">
         <v>622</v>
@@ -21056,7 +21056,7 @@
         <v>1806</v>
       </c>
       <c r="N274" s="5">
-        <v>5.6599</v>
+        <v>0.0005659899999999999</v>
       </c>
       <c r="O274" s="2" t="s">
         <v>622</v>
@@ -21109,7 +21109,7 @@
         <v>1807</v>
       </c>
       <c r="N275" s="9">
-        <v>5.6569</v>
+        <v>0.00056569</v>
       </c>
       <c r="O275" s="6" t="s">
         <v>622</v>
@@ -21162,7 +21162,7 @@
         <v>1808</v>
       </c>
       <c r="N276" s="5">
-        <v>5.6505</v>
+        <v>0.00056505</v>
       </c>
       <c r="O276" s="2" t="s">
         <v>622</v>
@@ -21215,7 +21215,7 @@
         <v>1809</v>
       </c>
       <c r="N277" s="9">
-        <v>5.6395</v>
+        <v>0.00056395</v>
       </c>
       <c r="O277" s="6" t="s">
         <v>622</v>
@@ -21268,7 +21268,7 @@
         <v>1810</v>
       </c>
       <c r="N278" s="5">
-        <v>5.6206</v>
+        <v>0.00056206</v>
       </c>
       <c r="O278" s="2" t="s">
         <v>622</v>
@@ -21321,7 +21321,7 @@
         <v>1811</v>
       </c>
       <c r="N279" s="9">
-        <v>5.568</v>
+        <v>0.0005568</v>
       </c>
       <c r="O279" s="6" t="s">
         <v>622</v>
@@ -21374,7 +21374,7 @@
         <v>1812</v>
       </c>
       <c r="N280" s="5">
-        <v>5.5647</v>
+        <v>0.00055647</v>
       </c>
       <c r="O280" s="2" t="s">
         <v>622</v>
@@ -21427,7 +21427,7 @@
         <v>1813</v>
       </c>
       <c r="N281" s="9">
-        <v>5.5512</v>
+        <v>0.00055512</v>
       </c>
       <c r="O281" s="6" t="s">
         <v>622</v>
@@ -21480,7 +21480,7 @@
         <v>1814</v>
       </c>
       <c r="N282" s="5">
-        <v>5.532</v>
+        <v>0.0005532</v>
       </c>
       <c r="O282" s="2" t="s">
         <v>622</v>
@@ -21533,7 +21533,7 @@
         <v>1815</v>
       </c>
       <c r="N283" s="9">
-        <v>5.5054</v>
+        <v>0.00055054</v>
       </c>
       <c r="O283" s="6" t="s">
         <v>622</v>
@@ -21586,7 +21586,7 @@
         <v>1816</v>
       </c>
       <c r="N284" s="5">
-        <v>5.3496</v>
+        <v>0.00053496</v>
       </c>
       <c r="O284" s="2" t="s">
         <v>622</v>
@@ -21639,7 +21639,7 @@
         <v>1817</v>
       </c>
       <c r="N285" s="9">
-        <v>5.3434</v>
+        <v>0.00053434</v>
       </c>
       <c r="O285" s="6" t="s">
         <v>622</v>
@@ -21692,7 +21692,7 @@
         <v>1818</v>
       </c>
       <c r="N286" s="5">
-        <v>5.3363</v>
+        <v>0.00053363</v>
       </c>
       <c r="O286" s="2" t="s">
         <v>622</v>
@@ -21745,7 +21745,7 @@
         <v>1819</v>
       </c>
       <c r="N287" s="9">
-        <v>5.3343</v>
+        <v>0.00053343</v>
       </c>
       <c r="O287" s="6" t="s">
         <v>622</v>
@@ -21798,7 +21798,7 @@
         <v>1820</v>
       </c>
       <c r="N288" s="5">
-        <v>5.2947</v>
+        <v>0.00052947</v>
       </c>
       <c r="O288" s="2" t="s">
         <v>622</v>
@@ -21851,7 +21851,7 @@
         <v>1821</v>
       </c>
       <c r="N289" s="9">
-        <v>5.2866</v>
+        <v>0.00052866</v>
       </c>
       <c r="O289" s="6" t="s">
         <v>622</v>
@@ -21904,7 +21904,7 @@
         <v>1822</v>
       </c>
       <c r="N290" s="5">
-        <v>5.2814</v>
+        <v>0.00052814</v>
       </c>
       <c r="O290" s="2" t="s">
         <v>622</v>
@@ -21957,7 +21957,7 @@
         <v>1823</v>
       </c>
       <c r="N291" s="9">
-        <v>5.2787</v>
+        <v>0.0005278700000000001</v>
       </c>
       <c r="O291" s="6" t="s">
         <v>622</v>
@@ -22010,7 +22010,7 @@
         <v>1824</v>
       </c>
       <c r="N292" s="5">
-        <v>5.2318</v>
+        <v>0.00052318</v>
       </c>
       <c r="O292" s="2" t="s">
         <v>622</v>
@@ -22063,7 +22063,7 @@
         <v>1825</v>
       </c>
       <c r="N293" s="9">
-        <v>5.2153</v>
+        <v>0.00052153</v>
       </c>
       <c r="O293" s="6" t="s">
         <v>622</v>
@@ -22116,7 +22116,7 @@
         <v>1826</v>
       </c>
       <c r="N294" s="5">
-        <v>5.2135</v>
+        <v>0.00052135</v>
       </c>
       <c r="O294" s="2" t="s">
         <v>622</v>
@@ -22169,7 +22169,7 @@
         <v>1827</v>
       </c>
       <c r="N295" s="9">
-        <v>5.2104</v>
+        <v>0.00052104</v>
       </c>
       <c r="O295" s="6" t="s">
         <v>622</v>
@@ -22222,7 +22222,7 @@
         <v>1828</v>
       </c>
       <c r="N296" s="5">
-        <v>5.1999</v>
+        <v>0.00051999</v>
       </c>
       <c r="O296" s="2" t="s">
         <v>622</v>
@@ -22275,7 +22275,7 @@
         <v>1829</v>
       </c>
       <c r="N297" s="9">
-        <v>5.1868</v>
+        <v>0.00051868</v>
       </c>
       <c r="O297" s="6" t="s">
         <v>622</v>
@@ -22328,7 +22328,7 @@
         <v>1830</v>
       </c>
       <c r="N298" s="5">
-        <v>5.1714</v>
+        <v>0.00051714</v>
       </c>
       <c r="O298" s="2" t="s">
         <v>622</v>
@@ -22381,7 +22381,7 @@
         <v>1831</v>
       </c>
       <c r="N299" s="9">
-        <v>5.1352</v>
+        <v>0.0005135200000000001</v>
       </c>
       <c r="O299" s="6" t="s">
         <v>622</v>
@@ -22434,7 +22434,7 @@
         <v>1832</v>
       </c>
       <c r="N300" s="5">
-        <v>5.1134</v>
+        <v>0.00051134</v>
       </c>
       <c r="O300" s="2" t="s">
         <v>622</v>
@@ -22487,7 +22487,7 @@
         <v>1833</v>
       </c>
       <c r="N301" s="9">
-        <v>5.0991</v>
+        <v>0.00050991</v>
       </c>
       <c r="O301" s="6" t="s">
         <v>622</v>
@@ -22540,7 +22540,7 @@
         <v>1834</v>
       </c>
       <c r="N302" s="5">
-        <v>5.0901</v>
+        <v>0.0005090100000000001</v>
       </c>
       <c r="O302" s="2" t="s">
         <v>622</v>
@@ -22593,7 +22593,7 @@
         <v>1835</v>
       </c>
       <c r="N303" s="9">
-        <v>5.0736</v>
+        <v>0.00050736</v>
       </c>
       <c r="O303" s="6" t="s">
         <v>622</v>
@@ -22646,7 +22646,7 @@
         <v>1836</v>
       </c>
       <c r="N304" s="5">
-        <v>5.0478</v>
+        <v>0.00050478</v>
       </c>
       <c r="O304" s="2" t="s">
         <v>622</v>
@@ -22699,7 +22699,7 @@
         <v>1837</v>
       </c>
       <c r="N305" s="9">
-        <v>4.9865</v>
+        <v>0.00049865</v>
       </c>
       <c r="O305" s="6" t="s">
         <v>622</v>
@@ -22752,7 +22752,7 @@
         <v>1838</v>
       </c>
       <c r="N306" s="5">
-        <v>4.9376</v>
+        <v>0.00049376</v>
       </c>
       <c r="O306" s="2" t="s">
         <v>622</v>
@@ -22805,7 +22805,7 @@
         <v>1839</v>
       </c>
       <c r="N307" s="9">
-        <v>4.9103</v>
+        <v>0.00049103</v>
       </c>
       <c r="O307" s="6" t="s">
         <v>622</v>
@@ -22858,7 +22858,7 @@
         <v>1840</v>
       </c>
       <c r="N308" s="5">
-        <v>4.9084</v>
+        <v>0.00049084</v>
       </c>
       <c r="O308" s="2" t="s">
         <v>622</v>
@@ -22911,7 +22911,7 @@
         <v>1841</v>
       </c>
       <c r="N309" s="9">
-        <v>4.9029</v>
+        <v>0.00049029</v>
       </c>
       <c r="O309" s="6" t="s">
         <v>622</v>
@@ -22964,7 +22964,7 @@
         <v>1842</v>
       </c>
       <c r="N310" s="5">
-        <v>4.8884</v>
+        <v>0.0004888399999999999</v>
       </c>
       <c r="O310" s="2" t="s">
         <v>622</v>
@@ -23017,7 +23017,7 @@
         <v>1843</v>
       </c>
       <c r="N311" s="9">
-        <v>4.8751</v>
+        <v>0.00048751</v>
       </c>
       <c r="O311" s="6" t="s">
         <v>622</v>
@@ -23070,7 +23070,7 @@
         <v>1844</v>
       </c>
       <c r="N312" s="5">
-        <v>4.8472</v>
+        <v>0.00048472</v>
       </c>
       <c r="O312" s="2" t="s">
         <v>622</v>
@@ -23123,7 +23123,7 @@
         <v>1845</v>
       </c>
       <c r="N313" s="9">
-        <v>4.8319</v>
+        <v>0.00048319</v>
       </c>
       <c r="O313" s="6" t="s">
         <v>622</v>
@@ -23176,7 +23176,7 @@
         <v>1846</v>
       </c>
       <c r="N314" s="5">
-        <v>4.8061</v>
+        <v>0.00048061</v>
       </c>
       <c r="O314" s="2" t="s">
         <v>622</v>
@@ -23229,7 +23229,7 @@
         <v>1847</v>
       </c>
       <c r="N315" s="9">
-        <v>4.7889</v>
+        <v>0.00047889</v>
       </c>
       <c r="O315" s="6" t="s">
         <v>622</v>
@@ -23282,7 +23282,7 @@
         <v>1848</v>
       </c>
       <c r="N316" s="5">
-        <v>4.7837</v>
+        <v>0.00047837</v>
       </c>
       <c r="O316" s="2" t="s">
         <v>622</v>
@@ -23335,7 +23335,7 @@
         <v>1849</v>
       </c>
       <c r="N317" s="9">
-        <v>4.756</v>
+        <v>0.0004756</v>
       </c>
       <c r="O317" s="6" t="s">
         <v>622</v>
@@ -23388,7 +23388,7 @@
         <v>1850</v>
       </c>
       <c r="N318" s="5">
-        <v>4.7242</v>
+        <v>0.00047242</v>
       </c>
       <c r="O318" s="2" t="s">
         <v>622</v>
@@ -23441,7 +23441,7 @@
         <v>1851</v>
       </c>
       <c r="N319" s="9">
-        <v>4.7169</v>
+        <v>0.00047169</v>
       </c>
       <c r="O319" s="6" t="s">
         <v>622</v>
@@ -23494,7 +23494,7 @@
         <v>1852</v>
       </c>
       <c r="N320" s="5">
-        <v>4.6946</v>
+        <v>0.00046946</v>
       </c>
       <c r="O320" s="2" t="s">
         <v>622</v>
@@ -23547,7 +23547,7 @@
         <v>1853</v>
       </c>
       <c r="N321" s="9">
-        <v>4.6652</v>
+        <v>0.00046652</v>
       </c>
       <c r="O321" s="6" t="s">
         <v>622</v>
@@ -23600,7 +23600,7 @@
         <v>1854</v>
       </c>
       <c r="N322" s="5">
-        <v>4.6031</v>
+        <v>0.00046031</v>
       </c>
       <c r="O322" s="2" t="s">
         <v>622</v>
@@ -23653,7 +23653,7 @@
         <v>1855</v>
       </c>
       <c r="N323" s="9">
-        <v>4.5475</v>
+        <v>0.00045475</v>
       </c>
       <c r="O323" s="6" t="s">
         <v>622</v>
@@ -23706,7 +23706,7 @@
         <v>1856</v>
       </c>
       <c r="N324" s="5">
-        <v>4.5457</v>
+        <v>0.00045457</v>
       </c>
       <c r="O324" s="2" t="s">
         <v>622</v>
@@ -23759,7 +23759,7 @@
         <v>1857</v>
       </c>
       <c r="N325" s="9">
-        <v>4.5401</v>
+        <v>0.00045401</v>
       </c>
       <c r="O325" s="6" t="s">
         <v>622</v>
@@ -23812,7 +23812,7 @@
         <v>1858</v>
       </c>
       <c r="N326" s="5">
-        <v>4.4913</v>
+        <v>0.00044913</v>
       </c>
       <c r="O326" s="2" t="s">
         <v>622</v>
@@ -23865,7 +23865,7 @@
         <v>1859</v>
       </c>
       <c r="N327" s="9">
-        <v>4.4874</v>
+        <v>0.00044874</v>
       </c>
       <c r="O327" s="6" t="s">
         <v>622</v>
@@ -23918,7 +23918,7 @@
         <v>1860</v>
       </c>
       <c r="N328" s="5">
-        <v>4.4674</v>
+        <v>0.00044674</v>
       </c>
       <c r="O328" s="2" t="s">
         <v>622</v>
@@ -23971,7 +23971,7 @@
         <v>1861</v>
       </c>
       <c r="N329" s="9">
-        <v>4.464</v>
+        <v>0.0004464</v>
       </c>
       <c r="O329" s="6" t="s">
         <v>622</v>
@@ -24024,7 +24024,7 @@
         <v>1862</v>
       </c>
       <c r="N330" s="5">
-        <v>4.4635</v>
+        <v>0.00044635</v>
       </c>
       <c r="O330" s="2" t="s">
         <v>622</v>
@@ -24077,7 +24077,7 @@
         <v>1863</v>
       </c>
       <c r="N331" s="9">
-        <v>4.4611</v>
+        <v>0.00044611</v>
       </c>
       <c r="O331" s="6" t="s">
         <v>622</v>
@@ -24130,7 +24130,7 @@
         <v>1864</v>
       </c>
       <c r="N332" s="5">
-        <v>4.4417</v>
+        <v>0.00044417</v>
       </c>
       <c r="O332" s="2" t="s">
         <v>622</v>
@@ -24183,7 +24183,7 @@
         <v>1865</v>
       </c>
       <c r="N333" s="9">
-        <v>4.341</v>
+        <v>0.0004341</v>
       </c>
       <c r="O333" s="6" t="s">
         <v>622</v>
@@ -24236,7 +24236,7 @@
         <v>1866</v>
       </c>
       <c r="N334" s="5">
-        <v>4.3384</v>
+        <v>0.00043384</v>
       </c>
       <c r="O334" s="2" t="s">
         <v>622</v>
@@ -24289,7 +24289,7 @@
         <v>1867</v>
       </c>
       <c r="N335" s="9">
-        <v>4.2814</v>
+        <v>0.00042814</v>
       </c>
       <c r="O335" s="6" t="s">
         <v>622</v>
@@ -24342,7 +24342,7 @@
         <v>1868</v>
       </c>
       <c r="N336" s="5">
-        <v>4.2503</v>
+        <v>0.00042503</v>
       </c>
       <c r="O336" s="2" t="s">
         <v>622</v>
@@ -24395,7 +24395,7 @@
         <v>1869</v>
       </c>
       <c r="N337" s="9">
-        <v>4.2363</v>
+        <v>0.00042363</v>
       </c>
       <c r="O337" s="6" t="s">
         <v>622</v>
@@ -24448,7 +24448,7 @@
         <v>1870</v>
       </c>
       <c r="N338" s="5">
-        <v>4.2095</v>
+        <v>0.00042095</v>
       </c>
       <c r="O338" s="2" t="s">
         <v>622</v>
@@ -24501,7 +24501,7 @@
         <v>1871</v>
       </c>
       <c r="N339" s="9">
-        <v>4.1782</v>
+        <v>0.00041782</v>
       </c>
       <c r="O339" s="6" t="s">
         <v>622</v>
@@ -24554,7 +24554,7 @@
         <v>1872</v>
       </c>
       <c r="N340" s="5">
-        <v>4.17</v>
+        <v>0.000417</v>
       </c>
       <c r="O340" s="2" t="s">
         <v>622</v>
@@ -24607,7 +24607,7 @@
         <v>1873</v>
       </c>
       <c r="N341" s="9">
-        <v>4.1118</v>
+        <v>0.00041118</v>
       </c>
       <c r="O341" s="6" t="s">
         <v>622</v>
@@ -24660,7 +24660,7 @@
         <v>1874</v>
       </c>
       <c r="N342" s="5">
-        <v>4.0654</v>
+        <v>0.00040654</v>
       </c>
       <c r="O342" s="2" t="s">
         <v>622</v>
@@ -24713,7 +24713,7 @@
         <v>1875</v>
       </c>
       <c r="N343" s="9">
-        <v>4.0483</v>
+        <v>0.00040483</v>
       </c>
       <c r="O343" s="6" t="s">
         <v>622</v>
@@ -24766,7 +24766,7 @@
         <v>1876</v>
       </c>
       <c r="N344" s="5">
-        <v>4.0418</v>
+        <v>0.00040418</v>
       </c>
       <c r="O344" s="2" t="s">
         <v>622</v>
@@ -24819,7 +24819,7 @@
         <v>1877</v>
       </c>
       <c r="N345" s="9">
-        <v>4.035</v>
+        <v>0.0004035</v>
       </c>
       <c r="O345" s="6" t="s">
         <v>622</v>
@@ -24872,7 +24872,7 @@
         <v>1878</v>
       </c>
       <c r="N346" s="5">
-        <v>3.9417</v>
+        <v>0.00039417</v>
       </c>
       <c r="O346" s="2" t="s">
         <v>622</v>
@@ -24925,7 +24925,7 @@
         <v>1879</v>
       </c>
       <c r="N347" s="9">
-        <v>3.9393</v>
+        <v>0.00039393</v>
       </c>
       <c r="O347" s="6" t="s">
         <v>622</v>
@@ -24978,7 +24978,7 @@
         <v>1880</v>
       </c>
       <c r="N348" s="5">
-        <v>3.9387</v>
+        <v>0.00039387</v>
       </c>
       <c r="O348" s="2" t="s">
         <v>622</v>
@@ -25031,7 +25031,7 @@
         <v>1881</v>
       </c>
       <c r="N349" s="9">
-        <v>3.9179</v>
+        <v>0.00039179</v>
       </c>
       <c r="O349" s="6" t="s">
         <v>622</v>
@@ -25084,7 +25084,7 @@
         <v>1882</v>
       </c>
       <c r="N350" s="5">
-        <v>3.9132</v>
+        <v>0.00039132</v>
       </c>
       <c r="O350" s="2" t="s">
         <v>622</v>
@@ -25137,7 +25137,7 @@
         <v>1883</v>
       </c>
       <c r="N351" s="9">
-        <v>3.9112</v>
+        <v>0.00039112</v>
       </c>
       <c r="O351" s="6" t="s">
         <v>622</v>
@@ -25190,7 +25190,7 @@
         <v>1884</v>
       </c>
       <c r="N352" s="5">
-        <v>3.9</v>
+        <v>0.00039</v>
       </c>
       <c r="O352" s="2" t="s">
         <v>622</v>
@@ -25243,7 +25243,7 @@
         <v>1885</v>
       </c>
       <c r="N353" s="9">
-        <v>3.8882</v>
+        <v>0.00038882</v>
       </c>
       <c r="O353" s="6" t="s">
         <v>622</v>
@@ -25296,7 +25296,7 @@
         <v>1886</v>
       </c>
       <c r="N354" s="5">
-        <v>3.8833</v>
+        <v>0.00038833</v>
       </c>
       <c r="O354" s="2" t="s">
         <v>622</v>
@@ -25349,7 +25349,7 @@
         <v>1887</v>
       </c>
       <c r="N355" s="9">
-        <v>3.8245</v>
+        <v>0.00038245</v>
       </c>
       <c r="O355" s="6" t="s">
         <v>622</v>
@@ -25402,7 +25402,7 @@
         <v>1888</v>
       </c>
       <c r="N356" s="5">
-        <v>3.8028</v>
+        <v>0.00038028</v>
       </c>
       <c r="O356" s="2" t="s">
         <v>622</v>
@@ -25455,7 +25455,7 @@
         <v>1889</v>
       </c>
       <c r="N357" s="9">
-        <v>3.7149</v>
+        <v>0.00037149</v>
       </c>
       <c r="O357" s="6" t="s">
         <v>622</v>
@@ -25508,7 +25508,7 @@
         <v>1890</v>
       </c>
       <c r="N358" s="5">
-        <v>3.7105</v>
+        <v>0.00037105</v>
       </c>
       <c r="O358" s="2" t="s">
         <v>622</v>
@@ -25561,7 +25561,7 @@
         <v>1891</v>
       </c>
       <c r="N359" s="9">
-        <v>3.692</v>
+        <v>0.0003692</v>
       </c>
       <c r="O359" s="6" t="s">
         <v>622</v>
@@ -25614,7 +25614,7 @@
         <v>1892</v>
       </c>
       <c r="N360" s="5">
-        <v>3.6856</v>
+        <v>0.00036856</v>
       </c>
       <c r="O360" s="2" t="s">
         <v>622</v>
@@ -25667,7 +25667,7 @@
         <v>1893</v>
       </c>
       <c r="N361" s="9">
-        <v>3.6632</v>
+        <v>0.00036632</v>
       </c>
       <c r="O361" s="6" t="s">
         <v>622</v>
@@ -25720,7 +25720,7 @@
         <v>1894</v>
       </c>
       <c r="N362" s="5">
-        <v>3.6619</v>
+        <v>0.00036619</v>
       </c>
       <c r="O362" s="2" t="s">
         <v>622</v>
@@ -25773,7 +25773,7 @@
         <v>1895</v>
       </c>
       <c r="N363" s="9">
-        <v>3.6502</v>
+        <v>0.00036502</v>
       </c>
       <c r="O363" s="6" t="s">
         <v>622</v>
@@ -25826,7 +25826,7 @@
         <v>1896</v>
       </c>
       <c r="N364" s="5">
-        <v>3.635</v>
+        <v>0.0003635</v>
       </c>
       <c r="O364" s="2" t="s">
         <v>622</v>
@@ -25879,7 +25879,7 @@
         <v>1897</v>
       </c>
       <c r="N365" s="9">
-        <v>3.6262</v>
+        <v>0.00036262</v>
       </c>
       <c r="O365" s="6" t="s">
         <v>622</v>
@@ -25932,7 +25932,7 @@
         <v>1898</v>
       </c>
       <c r="N366" s="5">
-        <v>3.6219</v>
+        <v>0.00036219</v>
       </c>
       <c r="O366" s="2" t="s">
         <v>622</v>
@@ -25985,7 +25985,7 @@
         <v>1899</v>
       </c>
       <c r="N367" s="9">
-        <v>3.6145</v>
+        <v>0.00036145</v>
       </c>
       <c r="O367" s="6" t="s">
         <v>622</v>
@@ -26038,7 +26038,7 @@
         <v>1900</v>
       </c>
       <c r="N368" s="5">
-        <v>3.5674</v>
+        <v>0.00035674</v>
       </c>
       <c r="O368" s="2" t="s">
         <v>622</v>
@@ -26091,7 +26091,7 @@
         <v>1901</v>
       </c>
       <c r="N369" s="9">
-        <v>3.4969</v>
+        <v>0.00034969</v>
       </c>
       <c r="O369" s="6" t="s">
         <v>622</v>
@@ -26144,7 +26144,7 @@
         <v>1902</v>
       </c>
       <c r="N370" s="5">
-        <v>3.4965</v>
+        <v>0.00034965</v>
       </c>
       <c r="O370" s="2" t="s">
         <v>622</v>
@@ -26197,7 +26197,7 @@
         <v>1903</v>
       </c>
       <c r="N371" s="9">
-        <v>3.4713</v>
+        <v>0.00034713</v>
       </c>
       <c r="O371" s="6" t="s">
         <v>622</v>
@@ -26250,7 +26250,7 @@
         <v>1904</v>
       </c>
       <c r="N372" s="5">
-        <v>3.4677</v>
+        <v>0.00034677</v>
       </c>
       <c r="O372" s="2" t="s">
         <v>622</v>
@@ -26303,7 +26303,7 @@
         <v>1905</v>
       </c>
       <c r="N373" s="9">
-        <v>3.4448</v>
+        <v>0.00034448</v>
       </c>
       <c r="O373" s="6" t="s">
         <v>622</v>
@@ -26356,7 +26356,7 @@
         <v>1906</v>
       </c>
       <c r="N374" s="5">
-        <v>3.4354</v>
+        <v>0.00034354</v>
       </c>
       <c r="O374" s="2" t="s">
         <v>622</v>
@@ -26409,7 +26409,7 @@
         <v>1907</v>
       </c>
       <c r="N375" s="9">
-        <v>3.4236</v>
+        <v>0.00034236</v>
       </c>
       <c r="O375" s="6" t="s">
         <v>622</v>
@@ -26462,7 +26462,7 @@
         <v>1908</v>
       </c>
       <c r="N376" s="5">
-        <v>3.3933</v>
+        <v>0.00033933</v>
       </c>
       <c r="O376" s="2" t="s">
         <v>622</v>
@@ -26515,7 +26515,7 @@
         <v>1909</v>
       </c>
       <c r="N377" s="9">
-        <v>3.3783</v>
+        <v>0.00033783</v>
       </c>
       <c r="O377" s="6" t="s">
         <v>622</v>
@@ -26568,7 +26568,7 @@
         <v>1910</v>
       </c>
       <c r="N378" s="5">
-        <v>3.3519</v>
+        <v>0.00033519</v>
       </c>
       <c r="O378" s="2" t="s">
         <v>622</v>
@@ -26621,7 +26621,7 @@
         <v>1911</v>
       </c>
       <c r="N379" s="9">
-        <v>3.3495</v>
+        <v>0.00033495</v>
       </c>
       <c r="O379" s="6" t="s">
         <v>622</v>
@@ -26674,7 +26674,7 @@
         <v>1912</v>
       </c>
       <c r="N380" s="5">
-        <v>3.3391</v>
+        <v>0.00033391</v>
       </c>
       <c r="O380" s="2" t="s">
         <v>622</v>
@@ -26727,7 +26727,7 @@
         <v>1913</v>
       </c>
       <c r="N381" s="9">
-        <v>3.3384</v>
+        <v>0.00033384</v>
       </c>
       <c r="O381" s="6" t="s">
         <v>622</v>
@@ -26780,7 +26780,7 @@
         <v>1914</v>
       </c>
       <c r="N382" s="5">
-        <v>3.3279</v>
+        <v>0.00033279</v>
       </c>
       <c r="O382" s="2" t="s">
         <v>622</v>
@@ -26833,7 +26833,7 @@
         <v>1915</v>
       </c>
       <c r="N383" s="9">
-        <v>3.3149</v>
+        <v>0.00033149</v>
       </c>
       <c r="O383" s="6" t="s">
         <v>622</v>
@@ -26886,7 +26886,7 @@
         <v>1916</v>
       </c>
       <c r="N384" s="5">
-        <v>3.3085</v>
+        <v>0.00033085</v>
       </c>
       <c r="O384" s="2" t="s">
         <v>622</v>
@@ -26939,7 +26939,7 @@
         <v>1917</v>
       </c>
       <c r="N385" s="9">
-        <v>3.308</v>
+        <v>0.0003308</v>
       </c>
       <c r="O385" s="6" t="s">
         <v>622</v>
@@ -26992,7 +26992,7 @@
         <v>1918</v>
       </c>
       <c r="N386" s="5">
-        <v>3.3047</v>
+        <v>0.00033047</v>
       </c>
       <c r="O386" s="2" t="s">
         <v>622</v>
@@ -27045,7 +27045,7 @@
         <v>1919</v>
       </c>
       <c r="N387" s="9">
-        <v>3.2995</v>
+        <v>0.00032995</v>
       </c>
       <c r="O387" s="6" t="s">
         <v>622</v>
@@ -27098,7 +27098,7 @@
         <v>1920</v>
       </c>
       <c r="N388" s="5">
-        <v>3.2773</v>
+        <v>0.00032773</v>
       </c>
       <c r="O388" s="2" t="s">
         <v>622</v>
@@ -27151,7 +27151,7 @@
         <v>1921</v>
       </c>
       <c r="N389" s="9">
-        <v>3.2593</v>
+        <v>0.00032593</v>
       </c>
       <c r="O389" s="6" t="s">
         <v>622</v>
@@ -27204,7 +27204,7 @@
         <v>1922</v>
       </c>
       <c r="N390" s="5">
-        <v>3.2233</v>
+        <v>0.00032233</v>
       </c>
       <c r="O390" s="2" t="s">
         <v>622</v>
@@ -27257,7 +27257,7 @@
         <v>1923</v>
       </c>
       <c r="N391" s="9">
-        <v>3.2222</v>
+        <v>0.00032222</v>
       </c>
       <c r="O391" s="6" t="s">
         <v>622</v>
@@ -27310,7 +27310,7 @@
         <v>1924</v>
       </c>
       <c r="N392" s="5">
-        <v>3.2133</v>
+        <v>0.00032133</v>
       </c>
       <c r="O392" s="2" t="s">
         <v>622</v>
@@ -27363,7 +27363,7 @@
         <v>1925</v>
       </c>
       <c r="N393" s="9">
-        <v>3.1972</v>
+        <v>0.00031972</v>
       </c>
       <c r="O393" s="6" t="s">
         <v>622</v>
@@ -27416,7 +27416,7 @@
         <v>1926</v>
       </c>
       <c r="N394" s="5">
-        <v>3.1957</v>
+        <v>0.00031957</v>
       </c>
       <c r="O394" s="2" t="s">
         <v>622</v>
@@ -27469,7 +27469,7 @@
         <v>1927</v>
       </c>
       <c r="N395" s="9">
-        <v>3.1956</v>
+        <v>0.00031956</v>
       </c>
       <c r="O395" s="6" t="s">
         <v>622</v>
@@ -27522,7 +27522,7 @@
         <v>1928</v>
       </c>
       <c r="N396" s="5">
-        <v>3.1309</v>
+        <v>0.00031309</v>
       </c>
       <c r="O396" s="2" t="s">
         <v>622</v>
@@ -27575,7 +27575,7 @@
         <v>1929</v>
       </c>
       <c r="N397" s="9">
-        <v>3.1174</v>
+        <v>0.00031174</v>
       </c>
       <c r="O397" s="6" t="s">
         <v>622</v>
@@ -27628,7 +27628,7 @@
         <v>1930</v>
       </c>
       <c r="N398" s="5">
-        <v>3.1141</v>
+        <v>0.00031141</v>
       </c>
       <c r="O398" s="2" t="s">
         <v>622</v>
@@ -27681,7 +27681,7 @@
         <v>1931</v>
       </c>
       <c r="N399" s="9">
-        <v>3.0498</v>
+        <v>0.00030498</v>
       </c>
       <c r="O399" s="6" t="s">
         <v>622</v>
@@ -27734,7 +27734,7 @@
         <v>1932</v>
       </c>
       <c r="N400" s="5">
-        <v>3.0252</v>
+        <v>0.00030252</v>
       </c>
       <c r="O400" s="2" t="s">
         <v>622</v>
@@ -27787,7 +27787,7 @@
         <v>1933</v>
       </c>
       <c r="N401" s="9">
-        <v>3.0175</v>
+        <v>0.00030175</v>
       </c>
       <c r="O401" s="6" t="s">
         <v>622</v>
@@ -27840,7 +27840,7 @@
         <v>1934</v>
       </c>
       <c r="N402" s="5">
-        <v>2.9894</v>
+        <v>0.00029894</v>
       </c>
       <c r="O402" s="2" t="s">
         <v>622</v>
@@ -27893,7 +27893,7 @@
         <v>1935</v>
       </c>
       <c r="N403" s="9">
-        <v>2.9826</v>
+        <v>0.00029826</v>
       </c>
       <c r="O403" s="6" t="s">
         <v>622</v>
@@ -27946,7 +27946,7 @@
         <v>1936</v>
       </c>
       <c r="N404" s="5">
-        <v>2.9167</v>
+        <v>0.00029167</v>
       </c>
       <c r="O404" s="2" t="s">
         <v>622</v>
@@ -27999,7 +27999,7 @@
         <v>1937</v>
       </c>
       <c r="N405" s="9">
-        <v>2.9115</v>
+        <v>0.00029115</v>
       </c>
       <c r="O405" s="6" t="s">
         <v>622</v>
@@ -28052,7 +28052,7 @@
         <v>1938</v>
       </c>
       <c r="N406" s="5">
-        <v>2.9107</v>
+        <v>0.00029107</v>
       </c>
       <c r="O406" s="2" t="s">
         <v>622</v>
@@ -28105,7 +28105,7 @@
         <v>1939</v>
       </c>
       <c r="N407" s="9">
-        <v>2.904</v>
+        <v>0.0002904</v>
       </c>
       <c r="O407" s="6" t="s">
         <v>622</v>
@@ -28158,7 +28158,7 @@
         <v>1940</v>
       </c>
       <c r="N408" s="5">
-        <v>2.8974</v>
+        <v>0.00028974</v>
       </c>
       <c r="O408" s="2" t="s">
         <v>622</v>
@@ -28211,7 +28211,7 @@
         <v>1941</v>
       </c>
       <c r="N409" s="9">
-        <v>2.8952</v>
+        <v>0.00028952</v>
       </c>
       <c r="O409" s="6" t="s">
         <v>622</v>
@@ -28264,7 +28264,7 @@
         <v>1942</v>
       </c>
       <c r="N410" s="5">
-        <v>2.8749</v>
+        <v>0.00028749</v>
       </c>
       <c r="O410" s="2" t="s">
         <v>622</v>
@@ -28317,7 +28317,7 @@
         <v>1943</v>
       </c>
       <c r="N411" s="9">
-        <v>2.8601</v>
+        <v>0.00028601</v>
       </c>
       <c r="O411" s="6" t="s">
         <v>622</v>
@@ -28370,7 +28370,7 @@
         <v>1944</v>
       </c>
       <c r="N412" s="5">
-        <v>2.8409</v>
+        <v>0.00028409</v>
       </c>
       <c r="O412" s="2" t="s">
         <v>622</v>
@@ -28423,7 +28423,7 @@
         <v>1945</v>
       </c>
       <c r="N413" s="9">
-        <v>2.8357</v>
+        <v>0.00028357</v>
       </c>
       <c r="O413" s="6" t="s">
         <v>622</v>
@@ -28476,7 +28476,7 @@
         <v>1946</v>
       </c>
       <c r="N414" s="5">
-        <v>2.8275</v>
+        <v>0.00028275</v>
       </c>
       <c r="O414" s="2" t="s">
         <v>622</v>
@@ -28529,7 +28529,7 @@
         <v>1947</v>
       </c>
       <c r="N415" s="9">
-        <v>2.8172</v>
+        <v>0.00028172</v>
       </c>
       <c r="O415" s="6" t="s">
         <v>622</v>
@@ -28582,7 +28582,7 @@
         <v>1948</v>
       </c>
       <c r="N416" s="5">
-        <v>2.8119</v>
+        <v>0.00028119</v>
       </c>
       <c r="O416" s="2" t="s">
         <v>622</v>
@@ -28635,7 +28635,7 @@
         <v>1949</v>
       </c>
       <c r="N417" s="9">
-        <v>2.7931</v>
+        <v>0.00027931</v>
       </c>
       <c r="O417" s="6" t="s">
         <v>622</v>
@@ -28688,7 +28688,7 @@
         <v>1950</v>
       </c>
       <c r="N418" s="5">
-        <v>2.7421</v>
+        <v>0.00027421</v>
       </c>
       <c r="O418" s="2" t="s">
         <v>622</v>
@@ -28741,7 +28741,7 @@
         <v>1951</v>
       </c>
       <c r="N419" s="9">
-        <v>2.7201</v>
+        <v>0.00027201</v>
       </c>
       <c r="O419" s="6" t="s">
         <v>622</v>
@@ -28794,7 +28794,7 @@
         <v>1952</v>
       </c>
       <c r="N420" s="5">
-        <v>2.7094</v>
+        <v>0.00027094</v>
       </c>
       <c r="O420" s="2" t="s">
         <v>622</v>
@@ -28847,7 +28847,7 @@
         <v>1953</v>
       </c>
       <c r="N421" s="9">
-        <v>2.6926</v>
+        <v>0.00026926</v>
       </c>
       <c r="O421" s="6" t="s">
         <v>622</v>
@@ -28900,7 +28900,7 @@
         <v>1954</v>
       </c>
       <c r="N422" s="5">
-        <v>2.6783</v>
+        <v>0.00026783</v>
       </c>
       <c r="O422" s="2" t="s">
         <v>622</v>
@@ -28953,7 +28953,7 @@
         <v>1955</v>
       </c>
       <c r="N423" s="9">
-        <v>2.6673</v>
+        <v>0.00026673</v>
       </c>
       <c r="O423" s="6" t="s">
         <v>622</v>
@@ -29006,7 +29006,7 @@
         <v>1956</v>
       </c>
       <c r="N424" s="5">
-        <v>2.6515</v>
+        <v>0.00026515</v>
       </c>
       <c r="O424" s="2" t="s">
         <v>622</v>
@@ -29059,7 +29059,7 @@
         <v>1957</v>
       </c>
       <c r="N425" s="9">
-        <v>2.6493</v>
+        <v>0.00026493</v>
       </c>
       <c r="O425" s="6" t="s">
         <v>622</v>
@@ -29112,7 +29112,7 @@
         <v>1958</v>
       </c>
       <c r="N426" s="5">
-        <v>2.6381</v>
+        <v>0.00026381</v>
       </c>
       <c r="O426" s="2" t="s">
         <v>622</v>
@@ -29165,7 +29165,7 @@
         <v>1959</v>
       </c>
       <c r="N427" s="9">
-        <v>2.6262</v>
+        <v>0.00026262</v>
       </c>
       <c r="O427" s="6" t="s">
         <v>622</v>
@@ -29218,7 +29218,7 @@
         <v>1960</v>
       </c>
       <c r="N428" s="5">
-        <v>2.6036</v>
+        <v>0.00026036</v>
       </c>
       <c r="O428" s="2" t="s">
         <v>622</v>
@@ -29271,7 +29271,7 @@
         <v>1961</v>
       </c>
       <c r="N429" s="9">
-        <v>2.6014</v>
+        <v>0.00026014</v>
       </c>
       <c r="O429" s="6" t="s">
         <v>622</v>
@@ -29324,7 +29324,7 @@
         <v>1962</v>
       </c>
       <c r="N430" s="5">
-        <v>2.5898</v>
+        <v>0.00025898</v>
       </c>
       <c r="O430" s="2" t="s">
         <v>622</v>
@@ -29377,7 +29377,7 @@
         <v>1963</v>
       </c>
       <c r="N431" s="9">
-        <v>2.57</v>
+        <v>0.000257</v>
       </c>
       <c r="O431" s="6" t="s">
         <v>622</v>
@@ -29430,7 +29430,7 @@
         <v>1964</v>
       </c>
       <c r="N432" s="5">
-        <v>2.5416</v>
+        <v>0.00025416</v>
       </c>
       <c r="O432" s="2" t="s">
         <v>622</v>
@@ -29483,7 +29483,7 @@
         <v>1965</v>
       </c>
       <c r="N433" s="9">
-        <v>2.5308</v>
+        <v>0.00025308</v>
       </c>
       <c r="O433" s="6" t="s">
         <v>622</v>
@@ -29536,7 +29536,7 @@
         <v>1966</v>
       </c>
       <c r="N434" s="5">
-        <v>2.507</v>
+        <v>0.0002507</v>
       </c>
       <c r="O434" s="2" t="s">
         <v>622</v>
@@ -29589,7 +29589,7 @@
         <v>1967</v>
       </c>
       <c r="N435" s="9">
-        <v>2.4957</v>
+        <v>0.00024957</v>
       </c>
       <c r="O435" s="6" t="s">
         <v>622</v>
@@ -29642,7 +29642,7 @@
         <v>1968</v>
       </c>
       <c r="N436" s="5">
-        <v>2.4743</v>
+        <v>0.00024743</v>
       </c>
       <c r="O436" s="2" t="s">
         <v>622</v>
@@ -29695,7 +29695,7 @@
         <v>1969</v>
       </c>
       <c r="N437" s="9">
-        <v>2.4655</v>
+        <v>0.00024655</v>
       </c>
       <c r="O437" s="6" t="s">
         <v>622</v>
@@ -29748,7 +29748,7 @@
         <v>1970</v>
       </c>
       <c r="N438" s="5">
-        <v>2.3364</v>
+        <v>0.00023364</v>
       </c>
       <c r="O438" s="2" t="s">
         <v>622</v>
@@ -29801,7 +29801,7 @@
         <v>1971</v>
       </c>
       <c r="N439" s="9">
-        <v>2.3335</v>
+        <v>0.00023335</v>
       </c>
       <c r="O439" s="6" t="s">
         <v>622</v>
@@ -29854,7 +29854,7 @@
         <v>1972</v>
       </c>
       <c r="N440" s="5">
-        <v>2.3149</v>
+        <v>0.00023149</v>
       </c>
       <c r="O440" s="2" t="s">
         <v>622</v>
@@ -29907,7 +29907,7 @@
         <v>1973</v>
       </c>
       <c r="N441" s="9">
-        <v>2.3012</v>
+        <v>0.00023012</v>
       </c>
       <c r="O441" s="6" t="s">
         <v>622</v>
@@ -29960,7 +29960,7 @@
         <v>1974</v>
       </c>
       <c r="N442" s="5">
-        <v>2.2634</v>
+        <v>0.00022634</v>
       </c>
       <c r="O442" s="2" t="s">
         <v>622</v>
@@ -30013,7 +30013,7 @@
         <v>1975</v>
       </c>
       <c r="N443" s="9">
-        <v>2.2185</v>
+        <v>0.00022185</v>
       </c>
       <c r="O443" s="6" t="s">
         <v>622</v>
@@ -30066,7 +30066,7 @@
         <v>1976</v>
       </c>
       <c r="N444" s="5">
-        <v>2.2117</v>
+        <v>0.00022117</v>
       </c>
       <c r="O444" s="2" t="s">
         <v>622</v>
@@ -30119,7 +30119,7 @@
         <v>1977</v>
       </c>
       <c r="N445" s="9">
-        <v>2.2062</v>
+        <v>0.00022062</v>
       </c>
       <c r="O445" s="6" t="s">
         <v>622</v>
@@ -30172,7 +30172,7 @@
         <v>1978</v>
       </c>
       <c r="N446" s="5">
-        <v>2.1885</v>
+        <v>0.00021885</v>
       </c>
       <c r="O446" s="2" t="s">
         <v>622</v>
@@ -30225,7 +30225,7 @@
         <v>1979</v>
       </c>
       <c r="N447" s="9">
-        <v>2.1479</v>
+        <v>0.00021479</v>
       </c>
       <c r="O447" s="6" t="s">
         <v>622</v>
@@ -30278,7 +30278,7 @@
         <v>1980</v>
       </c>
       <c r="N448" s="5">
-        <v>2.1421</v>
+        <v>0.00021421</v>
       </c>
       <c r="O448" s="2" t="s">
         <v>622</v>
@@ -30331,7 +30331,7 @@
         <v>1981</v>
       </c>
       <c r="N449" s="9">
-        <v>2.1414</v>
+        <v>0.00021414</v>
       </c>
       <c r="O449" s="6" t="s">
         <v>622</v>
@@ -30384,7 +30384,7 @@
         <v>1982</v>
       </c>
       <c r="N450" s="5">
-        <v>2.1164</v>
+        <v>0.00021164</v>
       </c>
       <c r="O450" s="2" t="s">
         <v>622</v>
@@ -30437,7 +30437,7 @@
         <v>1983</v>
       </c>
       <c r="N451" s="9">
-        <v>2.1084</v>
+        <v>0.00021084</v>
       </c>
       <c r="O451" s="6" t="s">
         <v>622</v>
@@ -30490,7 +30490,7 @@
         <v>1984</v>
       </c>
       <c r="N452" s="5">
-        <v>2.0875</v>
+        <v>0.00020875</v>
       </c>
       <c r="O452" s="2" t="s">
         <v>622</v>
@@ -30543,7 +30543,7 @@
         <v>1985</v>
       </c>
       <c r="N453" s="9">
-        <v>2.0858</v>
+        <v>0.00020858</v>
       </c>
       <c r="O453" s="6" t="s">
         <v>622</v>
@@ -30596,7 +30596,7 @@
         <v>1986</v>
       </c>
       <c r="N454" s="5">
-        <v>2.0705</v>
+        <v>0.00020705</v>
       </c>
       <c r="O454" s="2" t="s">
         <v>622</v>
@@ -30649,7 +30649,7 @@
         <v>1987</v>
       </c>
       <c r="N455" s="9">
-        <v>2.0562</v>
+        <v>0.00020562</v>
       </c>
       <c r="O455" s="6" t="s">
         <v>622</v>
@@ -30702,7 +30702,7 @@
         <v>1988</v>
       </c>
       <c r="N456" s="5">
-        <v>2.0453</v>
+        <v>0.00020453</v>
       </c>
       <c r="O456" s="2" t="s">
         <v>622</v>
@@ -30755,7 +30755,7 @@
         <v>1989</v>
       </c>
       <c r="N457" s="9">
-        <v>2.0354</v>
+        <v>0.00020354</v>
       </c>
       <c r="O457" s="6" t="s">
         <v>622</v>
@@ -30808,7 +30808,7 @@
         <v>1990</v>
       </c>
       <c r="N458" s="5">
-        <v>2.0271</v>
+        <v>0.00020271</v>
       </c>
       <c r="O458" s="2" t="s">
         <v>622</v>
@@ -30861,7 +30861,7 @@
         <v>1991</v>
       </c>
       <c r="N459" s="9">
-        <v>1.9959</v>
+        <v>0.00019959</v>
       </c>
       <c r="O459" s="6" t="s">
         <v>622</v>
@@ -30914,7 +30914,7 @@
         <v>1992</v>
       </c>
       <c r="N460" s="5">
-        <v>1.9488</v>
+        <v>0.00019488</v>
       </c>
       <c r="O460" s="2" t="s">
         <v>622</v>
@@ -30967,7 +30967,7 @@
         <v>1993</v>
       </c>
       <c r="N461" s="9">
-        <v>1.9362</v>
+        <v>0.00019362</v>
       </c>
       <c r="O461" s="6" t="s">
         <v>622</v>
@@ -31020,7 +31020,7 @@
         <v>1994</v>
       </c>
       <c r="N462" s="5">
-        <v>1.9139</v>
+        <v>0.00019139</v>
       </c>
       <c r="O462" s="2" t="s">
         <v>622</v>
@@ -31073,7 +31073,7 @@
         <v>1995</v>
       </c>
       <c r="N463" s="9">
-        <v>1.9133</v>
+        <v>0.00019133</v>
       </c>
       <c r="O463" s="6" t="s">
         <v>622</v>
@@ -31126,7 +31126,7 @@
         <v>1996</v>
       </c>
       <c r="N464" s="5">
-        <v>1.911</v>
+        <v>0.0001911</v>
       </c>
       <c r="O464" s="2" t="s">
         <v>622</v>
@@ -31179,7 +31179,7 @@
         <v>1997</v>
       </c>
       <c r="N465" s="9">
-        <v>1.9038</v>
+        <v>0.00019038</v>
       </c>
       <c r="O465" s="6" t="s">
         <v>622</v>
@@ -31232,7 +31232,7 @@
         <v>1998</v>
       </c>
       <c r="N466" s="5">
-        <v>1.8754</v>
+        <v>0.00018754</v>
       </c>
       <c r="O466" s="2" t="s">
         <v>622</v>
@@ -31285,7 +31285,7 @@
         <v>1999</v>
       </c>
       <c r="N467" s="9">
-        <v>1.8222</v>
+        <v>0.00018222</v>
       </c>
       <c r="O467" s="6" t="s">
         <v>622</v>
@@ -31338,7 +31338,7 @@
         <v>2000</v>
       </c>
       <c r="N468" s="5">
-        <v>1.81</v>
+        <v>0.000181</v>
       </c>
       <c r="O468" s="2" t="s">
         <v>622</v>
@@ -31391,7 +31391,7 @@
         <v>2001</v>
       </c>
       <c r="N469" s="9">
-        <v>1.7889</v>
+        <v>0.00017889</v>
       </c>
       <c r="O469" s="6" t="s">
         <v>622</v>
@@ -31444,7 +31444,7 @@
         <v>2002</v>
       </c>
       <c r="N470" s="5">
-        <v>1.7704</v>
+        <v>0.00017704</v>
       </c>
       <c r="O470" s="2" t="s">
         <v>622</v>
@@ -31497,7 +31497,7 @@
         <v>2003</v>
       </c>
       <c r="N471" s="9">
-        <v>1.7472</v>
+        <v>0.00017472</v>
       </c>
       <c r="O471" s="6" t="s">
         <v>622</v>
@@ -31550,7 +31550,7 @@
         <v>2004</v>
       </c>
       <c r="N472" s="5">
-        <v>1.7149</v>
+        <v>0.00017149</v>
       </c>
       <c r="O472" s="2" t="s">
         <v>622</v>
@@ -31603,7 +31603,7 @@
         <v>2005</v>
       </c>
       <c r="N473" s="9">
-        <v>1.6919</v>
+        <v>0.00016919</v>
       </c>
       <c r="O473" s="6" t="s">
         <v>622</v>
@@ -31656,7 +31656,7 @@
         <v>2006</v>
       </c>
       <c r="N474" s="5">
-        <v>1.666</v>
+        <v>0.0001666</v>
       </c>
       <c r="O474" s="2" t="s">
         <v>622</v>
@@ -31709,7 +31709,7 @@
         <v>2007</v>
       </c>
       <c r="N475" s="9">
-        <v>1.6263</v>
+        <v>0.00016263</v>
       </c>
       <c r="O475" s="6" t="s">
         <v>622</v>
@@ -31762,7 +31762,7 @@
         <v>2008</v>
       </c>
       <c r="N476" s="5">
-        <v>1.5464</v>
+        <v>0.00015464</v>
       </c>
       <c r="O476" s="2" t="s">
         <v>622</v>
@@ -31815,7 +31815,7 @@
         <v>2009</v>
       </c>
       <c r="N477" s="9">
-        <v>1.5189</v>
+        <v>0.00015189</v>
       </c>
       <c r="O477" s="6" t="s">
         <v>622</v>
@@ -31868,7 +31868,7 @@
         <v>2010</v>
       </c>
       <c r="N478" s="5">
-        <v>1.4546</v>
+        <v>0.00014546</v>
       </c>
       <c r="O478" s="2" t="s">
         <v>622</v>
@@ -31921,7 +31921,7 @@
         <v>2011</v>
       </c>
       <c r="N479" s="9">
-        <v>1.4455</v>
+        <v>0.00014455</v>
       </c>
       <c r="O479" s="6" t="s">
         <v>622</v>
@@ -31974,7 +31974,7 @@
         <v>2012</v>
       </c>
       <c r="N480" s="5">
-        <v>1.4179</v>
+        <v>0.00014179</v>
       </c>
       <c r="O480" s="2" t="s">
         <v>622</v>
@@ -32027,7 +32027,7 @@
         <v>2013</v>
       </c>
       <c r="N481" s="9">
-        <v>1.4044</v>
+        <v>0.00014044</v>
       </c>
       <c r="O481" s="6" t="s">
         <v>622</v>
@@ -32080,7 +32080,7 @@
         <v>2014</v>
       </c>
       <c r="N482" s="5">
-        <v>1.366</v>
+        <v>0.0001366</v>
       </c>
       <c r="O482" s="2" t="s">
         <v>622</v>
@@ -32133,7 +32133,7 @@
         <v>2015</v>
       </c>
       <c r="N483" s="9">
-        <v>1.3624</v>
+        <v>0.00013624</v>
       </c>
       <c r="O483" s="6" t="s">
         <v>622</v>
@@ -32186,7 +32186,7 @@
         <v>2016</v>
       </c>
       <c r="N484" s="5">
-        <v>1.3557</v>
+        <v>0.00013557</v>
       </c>
       <c r="O484" s="2" t="s">
         <v>622</v>
@@ -32239,7 +32239,7 @@
         <v>2017</v>
       </c>
       <c r="N485" s="9">
-        <v>1.3471</v>
+        <v>0.00013471</v>
       </c>
       <c r="O485" s="6" t="s">
         <v>622</v>
@@ -32292,7 +32292,7 @@
         <v>2018</v>
       </c>
       <c r="N486" s="5">
-        <v>1.3429</v>
+        <v>0.00013429</v>
       </c>
       <c r="O486" s="2" t="s">
         <v>622</v>
@@ -32345,7 +32345,7 @@
         <v>2019</v>
       </c>
       <c r="N487" s="9">
-        <v>1.3354</v>
+        <v>0.00013354</v>
       </c>
       <c r="O487" s="6" t="s">
         <v>622</v>
@@ -32398,7 +32398,7 @@
         <v>2020</v>
       </c>
       <c r="N488" s="5">
-        <v>1.3265</v>
+        <v>0.00013265</v>
       </c>
       <c r="O488" s="2" t="s">
         <v>622</v>
@@ -32451,7 +32451,7 @@
         <v>2021</v>
       </c>
       <c r="N489" s="9">
-        <v>1.3251</v>
+        <v>0.00013251</v>
       </c>
       <c r="O489" s="6" t="s">
         <v>622</v>
@@ -32504,7 +32504,7 @@
         <v>2022</v>
       </c>
       <c r="N490" s="5">
-        <v>1.3139</v>
+        <v>0.00013139</v>
       </c>
       <c r="O490" s="2" t="s">
         <v>622</v>
@@ -32557,7 +32557,7 @@
         <v>2023</v>
       </c>
       <c r="N491" s="9">
-        <v>1.3122</v>
+        <v>0.00013122</v>
       </c>
       <c r="O491" s="6" t="s">
         <v>622</v>
@@ -32610,7 +32610,7 @@
         <v>2024</v>
       </c>
       <c r="N492" s="5">
-        <v>1.3118</v>
+        <v>0.00013118</v>
       </c>
       <c r="O492" s="2" t="s">
         <v>622</v>
@@ -32663,7 +32663,7 @@
         <v>2025</v>
       </c>
       <c r="N493" s="9">
-        <v>1.2976</v>
+        <v>0.00012976</v>
       </c>
       <c r="O493" s="6" t="s">
         <v>622</v>
@@ -32716,7 +32716,7 @@
         <v>2026</v>
       </c>
       <c r="N494" s="5">
-        <v>1.2758</v>
+        <v>0.00012758</v>
       </c>
       <c r="O494" s="2" t="s">
         <v>622</v>
@@ -32769,7 +32769,7 @@
         <v>2027</v>
       </c>
       <c r="N495" s="9">
-        <v>1.2624</v>
+        <v>0.00012624</v>
       </c>
       <c r="O495" s="6" t="s">
         <v>622</v>
@@ -32822,7 +32822,7 @@
         <v>2028</v>
       </c>
       <c r="N496" s="5">
-        <v>1.1689</v>
+        <v>0.00011689</v>
       </c>
       <c r="O496" s="2" t="s">
         <v>622</v>
@@ -32875,7 +32875,7 @@
         <v>2029</v>
       </c>
       <c r="N497" s="9">
-        <v>1.1672</v>
+        <v>0.00011672</v>
       </c>
       <c r="O497" s="6" t="s">
         <v>622</v>
@@ -32928,7 +32928,7 @@
         <v>2030</v>
       </c>
       <c r="N498" s="5">
-        <v>1.0843</v>
+        <v>0.00010843</v>
       </c>
       <c r="O498" s="2" t="s">
         <v>622</v>
@@ -32981,7 +32981,7 @@
         <v>2031</v>
       </c>
       <c r="N499" s="9">
-        <v>1.0728</v>
+        <v>0.00010728</v>
       </c>
       <c r="O499" s="6" t="s">
         <v>622</v>
@@ -33034,7 +33034,7 @@
         <v>2032</v>
       </c>
       <c r="N500" s="5">
-        <v>0.9738</v>
+        <v>9.738000000000001E-05</v>
       </c>
       <c r="O500" s="2" t="s">
         <v>622</v>
@@ -33087,7 +33087,7 @@
         <v>2033</v>
       </c>
       <c r="N501" s="9">
-        <v>0.9479</v>
+        <v>9.478999999999999E-05</v>
       </c>
       <c r="O501" s="6" t="s">
         <v>622</v>
@@ -33140,7 +33140,7 @@
         <v>2034</v>
       </c>
       <c r="N502" s="5">
-        <v>0.7506</v>
+        <v>7.506E-05</v>
       </c>
       <c r="O502" s="2" t="s">
         <v>622</v>
@@ -33193,7 +33193,7 @@
         <v>2035</v>
       </c>
       <c r="N503" s="9">
-        <v>0.6954</v>
+        <v>6.954E-05</v>
       </c>
       <c r="O503" s="6" t="s">
         <v>622</v>
@@ -33246,7 +33246,7 @@
         <v>2036</v>
       </c>
       <c r="N504" s="5">
-        <v>0.5661</v>
+        <v>5.661E-05</v>
       </c>
       <c r="O504" s="2" t="s">
         <v>622</v>
@@ -33299,7 +33299,7 @@
         <v>2037</v>
       </c>
       <c r="N505" s="9">
-        <v>0.5358000000000001</v>
+        <v>5.358E-05</v>
       </c>
       <c r="O505" s="6" t="s">
         <v>622</v>
@@ -33345,8 +33345,8 @@
       <c r="B2" s="4">
         <v>504</v>
       </c>
-      <c r="C2" s="3">
-        <v>9994.930200000001</v>
+      <c r="C2" s="5">
+        <v>0.999493</v>
       </c>
     </row>
   </sheetData>
